--- a/research/traditional_assets/database/data/estonia/estonia_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_retail_special_lines.xlsx
@@ -1127,43 +1127,43 @@
         <v>32.1428571428571</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>809.805120397776</v>
       </c>
       <c r="G2">
         <v>0.329255319148936</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0235053191489362</v>
       </c>
       <c r="I2">
         <v>0.140076940484272</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>38</v>
       </c>
       <c r="L2">
-        <v>44.1914592509282</v>
+        <v>43.7493773250823</v>
       </c>
       <c r="M2">
         <v>-1.41</v>
       </c>
       <c r="N2">
-        <v>-1.40854074907182</v>
+        <v>-1.40872267491769</v>
       </c>
       <c r="O2">
         <v>6.19</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.4419</v>
       </c>
       <c r="Q2">
         <v>0.0960402733860421</v>
       </c>
       <c r="R2">
-        <v>0.0973114558269409</v>
+        <v>0.09715283291528699</v>
       </c>
       <c r="S2">
         <v>0.0470274039176792</v>
@@ -1185,13 +1185,13 @@
         <v>0.104024211859968</v>
       </c>
       <c r="X2">
-        <v>0.0973114558269409</v>
+        <v>0.09772771001544139</v>
       </c>
       <c r="Y2">
         <v>1.10449178380622</v>
       </c>
       <c r="Z2">
-        <v>0.977153282376524</v>
+        <v>0.98504947051694</v>
       </c>
       <c r="AA2">
         <v>6.19</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09731145582694091</v>
+        <v>0.09715283291528704</v>
       </c>
       <c r="C2">
-        <v>44.19145925092818</v>
+        <v>43.74937732508231</v>
       </c>
       <c r="D2">
-        <v>-1.408540749071816</v>
+        <v>-1.408722674917689</v>
       </c>
       <c r="E2">
-        <v>-6.19</v>
+        <v>-5.748100000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4419</v>
       </c>
       <c r="G2">
         <v>45.6</v>
@@ -1445,28 +1445,28 @@
         <v>18</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02222757</v>
       </c>
       <c r="N2">
-        <v>18</v>
+        <v>17.97777243</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.595554486000001</v>
       </c>
       <c r="P2">
-        <v>14.4</v>
+        <v>14.382217944</v>
       </c>
       <c r="Q2">
-        <v>15.2</v>
+        <v>15.182217944</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09731145582694091</v>
+        <v>0.09772771001544145</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765235</v>
+        <v>0.9850494705169399</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>809.8051203977764</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09715283291528704</v>
+        <v>0.09699421000363313</v>
       </c>
       <c r="C3">
-        <v>43.74937732508231</v>
+        <v>43.30729535223561</v>
       </c>
       <c r="D3">
-        <v>-1.408722674917689</v>
+        <v>-1.408904647764387</v>
       </c>
       <c r="E3">
-        <v>-5.748100000000001</v>
+        <v>-5.3062</v>
       </c>
       <c r="F3">
-        <v>0.4419</v>
+        <v>0.8837999999999999</v>
       </c>
       <c r="G3">
         <v>45.6</v>
@@ -1527,28 +1527,28 @@
         <v>18</v>
       </c>
       <c r="M3">
-        <v>0.02222757</v>
+        <v>0.04445514</v>
       </c>
       <c r="N3">
-        <v>17.97777243</v>
+        <v>17.95554486</v>
       </c>
       <c r="O3">
-        <v>3.595554486000001</v>
+        <v>3.591108972</v>
       </c>
       <c r="P3">
-        <v>14.382217944</v>
+        <v>14.364435888</v>
       </c>
       <c r="Q3">
-        <v>15.182217944</v>
+        <v>15.164435888</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09772771001544145</v>
+        <v>0.09815245918738076</v>
       </c>
       <c r="T3">
-        <v>0.9850494705169399</v>
+        <v>0.9931068053540995</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>809.8051203977764</v>
+        <v>404.9025601988882</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09699421000363313</v>
+        <v>0.09683558709197926</v>
       </c>
       <c r="C4">
-        <v>43.30729535223561</v>
+        <v>42.86521333236988</v>
       </c>
       <c r="D4">
-        <v>-1.408904647764387</v>
+        <v>-1.409086667630127</v>
       </c>
       <c r="E4">
-        <v>-5.3062</v>
+        <v>-4.8643</v>
       </c>
       <c r="F4">
-        <v>0.8837999999999999</v>
+        <v>1.3257</v>
       </c>
       <c r="G4">
         <v>45.6</v>
@@ -1609,28 +1609,28 @@
         <v>18</v>
       </c>
       <c r="M4">
-        <v>0.04445514</v>
+        <v>0.06668270999999999</v>
       </c>
       <c r="N4">
-        <v>17.95554486</v>
+        <v>17.93331729</v>
       </c>
       <c r="O4">
-        <v>3.591108972</v>
+        <v>3.586663458</v>
       </c>
       <c r="P4">
-        <v>14.364435888</v>
+        <v>14.346653832</v>
       </c>
       <c r="Q4">
-        <v>15.164435888</v>
+        <v>15.146653832</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09815245918738076</v>
+        <v>0.09858596607420542</v>
       </c>
       <c r="T4">
-        <v>0.9931068053540995</v>
+        <v>1.001330270806458</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>404.9025601988882</v>
+        <v>269.9350401325921</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09683558709197926</v>
+        <v>0.09667696418032538</v>
       </c>
       <c r="C5">
-        <v>42.86521333236988</v>
+        <v>42.42313126546686</v>
       </c>
       <c r="D5">
-        <v>-1.409086667630127</v>
+        <v>-1.409268734533135</v>
       </c>
       <c r="E5">
-        <v>-4.8643</v>
+        <v>-4.422400000000001</v>
       </c>
       <c r="F5">
-        <v>1.3257</v>
+        <v>1.7676</v>
       </c>
       <c r="G5">
         <v>45.6</v>
@@ -1691,28 +1691,28 @@
         <v>18</v>
       </c>
       <c r="M5">
-        <v>0.06668270999999999</v>
+        <v>0.08891027999999999</v>
       </c>
       <c r="N5">
-        <v>17.93331729</v>
+        <v>17.91108972</v>
       </c>
       <c r="O5">
-        <v>3.586663458</v>
+        <v>3.582217944</v>
       </c>
       <c r="P5">
-        <v>14.346653832</v>
+        <v>14.328871776</v>
       </c>
       <c r="Q5">
-        <v>15.146653832</v>
+        <v>15.128871776</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09858596607420542</v>
+        <v>0.09902850435450561</v>
       </c>
       <c r="T5">
-        <v>1.001330270806458</v>
+        <v>1.009725058455741</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>269.9350401325921</v>
+        <v>202.4512800994441</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09667696418032538</v>
+        <v>0.09651834126867148</v>
       </c>
       <c r="C6">
-        <v>42.42313126546686</v>
+        <v>41.98104915150836</v>
       </c>
       <c r="D6">
-        <v>-1.409268734533135</v>
+        <v>-1.409450848491645</v>
       </c>
       <c r="E6">
-        <v>-4.422400000000001</v>
+        <v>-3.980500000000001</v>
       </c>
       <c r="F6">
-        <v>1.7676</v>
+        <v>2.2095</v>
       </c>
       <c r="G6">
         <v>45.6</v>
@@ -1773,28 +1773,28 @@
         <v>18</v>
       </c>
       <c r="M6">
-        <v>0.08891027999999999</v>
+        <v>0.11113785</v>
       </c>
       <c r="N6">
-        <v>17.91108972</v>
+        <v>17.88886215</v>
       </c>
       <c r="O6">
-        <v>3.582217944</v>
+        <v>3.57777243</v>
       </c>
       <c r="P6">
-        <v>14.328871776</v>
+        <v>14.31108972</v>
       </c>
       <c r="Q6">
-        <v>15.128871776</v>
+        <v>15.11108972</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09902850435450561</v>
+        <v>0.09948035923018052</v>
       </c>
       <c r="T6">
-        <v>1.009725058455741</v>
+        <v>1.018296578476588</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>202.4512800994441</v>
+        <v>161.9610240795553</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09651834126867148</v>
+        <v>0.09635971835701762</v>
       </c>
       <c r="C7">
-        <v>41.98104915150836</v>
+        <v>41.5389669904761</v>
       </c>
       <c r="D7">
-        <v>-1.409450848491645</v>
+        <v>-1.409633009523902</v>
       </c>
       <c r="E7">
-        <v>-3.980500000000001</v>
+        <v>-3.5386</v>
       </c>
       <c r="F7">
-        <v>2.2095</v>
+        <v>2.6514</v>
       </c>
       <c r="G7">
         <v>45.6</v>
@@ -1855,28 +1855,28 @@
         <v>18</v>
       </c>
       <c r="M7">
-        <v>0.11113785</v>
+        <v>0.13336542</v>
       </c>
       <c r="N7">
-        <v>17.88886215</v>
+        <v>17.86663458</v>
       </c>
       <c r="O7">
-        <v>3.57777243</v>
+        <v>3.573326916</v>
       </c>
       <c r="P7">
-        <v>14.31108972</v>
+        <v>14.293307664</v>
       </c>
       <c r="Q7">
-        <v>15.11108972</v>
+        <v>15.093307664</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09948035923018052</v>
+        <v>0.09994182803938045</v>
       </c>
       <c r="T7">
-        <v>1.018296578476588</v>
+        <v>1.027050471263836</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>161.9610240795553</v>
+        <v>134.967520066296</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09635971835701762</v>
+        <v>0.09620109544536373</v>
       </c>
       <c r="C8">
-        <v>41.5389669904761</v>
+        <v>41.09688478235184</v>
       </c>
       <c r="D8">
-        <v>-1.409633009523902</v>
+        <v>-1.409815217648162</v>
       </c>
       <c r="E8">
-        <v>-3.538600000000001</v>
+        <v>-3.096700000000001</v>
       </c>
       <c r="F8">
-        <v>2.6514</v>
+        <v>3.0933</v>
       </c>
       <c r="G8">
         <v>45.6</v>
@@ -1937,28 +1937,28 @@
         <v>18</v>
       </c>
       <c r="M8">
-        <v>0.13336542</v>
+        <v>0.15559299</v>
       </c>
       <c r="N8">
-        <v>17.86663458</v>
+        <v>17.84440701</v>
       </c>
       <c r="O8">
-        <v>3.573326916</v>
+        <v>3.568881402000001</v>
       </c>
       <c r="P8">
-        <v>14.293307664</v>
+        <v>14.275525608</v>
       </c>
       <c r="Q8">
-        <v>15.093307664</v>
+        <v>15.075525608</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09994182803938045</v>
+        <v>0.1004132209089933</v>
       </c>
       <c r="T8">
-        <v>1.027050471263836</v>
+        <v>1.035992619809949</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>134.9675200662961</v>
+        <v>115.6864457711109</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09620109544536373</v>
+        <v>0.09604247253370986</v>
       </c>
       <c r="C9">
-        <v>41.09688478235184</v>
+        <v>40.65480252711731</v>
       </c>
       <c r="D9">
-        <v>-1.409815217648162</v>
+        <v>-1.409997472882686</v>
       </c>
       <c r="E9">
-        <v>-3.0967</v>
+        <v>-2.654800000000001</v>
       </c>
       <c r="F9">
-        <v>3.0933</v>
+        <v>3.5352</v>
       </c>
       <c r="G9">
         <v>45.6</v>
@@ -2019,28 +2019,28 @@
         <v>18</v>
       </c>
       <c r="M9">
-        <v>0.15559299</v>
+        <v>0.17782056</v>
       </c>
       <c r="N9">
-        <v>17.84440701</v>
+        <v>17.82217944</v>
       </c>
       <c r="O9">
-        <v>3.568881402000001</v>
+        <v>3.564435888</v>
       </c>
       <c r="P9">
-        <v>14.275525608</v>
+        <v>14.257743552</v>
       </c>
       <c r="Q9">
-        <v>15.075525608</v>
+        <v>15.057743552</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1004132209089933</v>
+        <v>0.1008948614496846</v>
       </c>
       <c r="T9">
-        <v>1.035992619809949</v>
+        <v>1.045129162889673</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>115.6864457711109</v>
+        <v>101.225640049722</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09604247253370986</v>
+        <v>0.09588384962205597</v>
       </c>
       <c r="C10">
-        <v>40.65480252711731</v>
+        <v>40.21272022475425</v>
       </c>
       <c r="D10">
-        <v>-1.409997472882686</v>
+        <v>-1.410179775245749</v>
       </c>
       <c r="E10">
-        <v>-2.654800000000001</v>
+        <v>-2.212900000000001</v>
       </c>
       <c r="F10">
-        <v>3.5352</v>
+        <v>3.9771</v>
       </c>
       <c r="G10">
         <v>45.6</v>
@@ -2101,28 +2101,28 @@
         <v>18</v>
       </c>
       <c r="M10">
-        <v>0.17782056</v>
+        <v>0.20004813</v>
       </c>
       <c r="N10">
-        <v>17.82217944</v>
+        <v>17.79995187</v>
       </c>
       <c r="O10">
-        <v>3.564435888</v>
+        <v>3.559990374</v>
       </c>
       <c r="P10">
-        <v>14.257743552</v>
+        <v>14.239961496</v>
       </c>
       <c r="Q10">
-        <v>15.057743552</v>
+        <v>15.039961496</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1008948614496846</v>
+        <v>0.1013870874967648</v>
       </c>
       <c r="T10">
-        <v>1.045129162889673</v>
+        <v>1.054466509114007</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>101.225640049722</v>
+        <v>89.97834671086405</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09588384962205597</v>
+        <v>0.09572522671040208</v>
       </c>
       <c r="C11">
-        <v>40.21272022475425</v>
+        <v>39.77063787524438</v>
       </c>
       <c r="D11">
-        <v>-1.410179775245749</v>
+        <v>-1.410362124755632</v>
       </c>
       <c r="E11">
-        <v>-2.212900000000001</v>
+        <v>-1.771000000000001</v>
       </c>
       <c r="F11">
-        <v>3.9771</v>
+        <v>4.419</v>
       </c>
       <c r="G11">
         <v>45.6</v>
@@ -2183,28 +2183,28 @@
         <v>18</v>
       </c>
       <c r="M11">
-        <v>0.20004813</v>
+        <v>0.2222757</v>
       </c>
       <c r="N11">
-        <v>17.79995187</v>
+        <v>17.7777243</v>
       </c>
       <c r="O11">
-        <v>3.559990374</v>
+        <v>3.55554486</v>
       </c>
       <c r="P11">
-        <v>14.239961496</v>
+        <v>14.22217944</v>
       </c>
       <c r="Q11">
-        <v>15.039961496</v>
+        <v>15.02217944</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1013870874967648</v>
+        <v>0.1018902519004468</v>
       </c>
       <c r="T11">
-        <v>1.054466509114007</v>
+        <v>1.064011351921103</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>89.97834671086405</v>
+        <v>80.98051203977764</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09572522671040211</v>
+        <v>0.09556660379874821</v>
       </c>
       <c r="C12">
-        <v>39.77063787524438</v>
+        <v>39.32855547856937</v>
       </c>
       <c r="D12">
-        <v>-1.410362124755632</v>
+        <v>-1.410544521430629</v>
       </c>
       <c r="E12">
-        <v>-1.771000000000001</v>
+        <v>-1.3291</v>
       </c>
       <c r="F12">
-        <v>4.419</v>
+        <v>4.8609</v>
       </c>
       <c r="G12">
         <v>45.6</v>
@@ -2265,28 +2265,28 @@
         <v>18</v>
       </c>
       <c r="M12">
-        <v>0.2222757</v>
+        <v>0.24450327</v>
       </c>
       <c r="N12">
-        <v>17.7777243</v>
+        <v>17.75549673</v>
       </c>
       <c r="O12">
-        <v>3.55554486</v>
+        <v>3.551099346</v>
       </c>
       <c r="P12">
-        <v>14.22217944</v>
+        <v>14.204397384</v>
       </c>
       <c r="Q12">
-        <v>15.02217944</v>
+        <v>15.004397384</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1018902519004468</v>
+        <v>0.10240472336938</v>
       </c>
       <c r="T12">
-        <v>1.064011351921104</v>
+        <v>1.073770685577798</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>80.98051203977764</v>
+        <v>73.61864730888875</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09556660379874821</v>
+        <v>0.09540798088709432</v>
       </c>
       <c r="C13">
-        <v>39.32855547856937</v>
+        <v>38.88647303471097</v>
       </c>
       <c r="D13">
-        <v>-1.410544521430629</v>
+        <v>-1.410726965289039</v>
       </c>
       <c r="E13">
-        <v>-1.3291</v>
+        <v>-0.8872000000000009</v>
       </c>
       <c r="F13">
-        <v>4.8609</v>
+        <v>5.3028</v>
       </c>
       <c r="G13">
         <v>45.6</v>
@@ -2347,28 +2347,28 @@
         <v>18</v>
       </c>
       <c r="M13">
-        <v>0.24450327</v>
+        <v>0.26673084</v>
       </c>
       <c r="N13">
-        <v>17.75549673</v>
+        <v>17.73326916</v>
       </c>
       <c r="O13">
-        <v>3.551099346</v>
+        <v>3.546653832</v>
       </c>
       <c r="P13">
-        <v>14.204397384</v>
+        <v>14.186615328</v>
       </c>
       <c r="Q13">
-        <v>15.004397384</v>
+        <v>14.986615328</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.10240472336938</v>
+        <v>0.1029308873716981</v>
       </c>
       <c r="T13">
-        <v>1.073770685577798</v>
+        <v>1.083751822272144</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>73.61864730888875</v>
+        <v>67.48376003314803</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09540798088709432</v>
+        <v>0.09524935797544044</v>
       </c>
       <c r="C14">
-        <v>38.88647303471097</v>
+        <v>38.44439054365083</v>
       </c>
       <c r="D14">
-        <v>-1.410726965289039</v>
+        <v>-1.410909456349174</v>
       </c>
       <c r="E14">
-        <v>-0.8872000000000009</v>
+        <v>-0.4453000000000005</v>
       </c>
       <c r="F14">
-        <v>5.3028</v>
+        <v>5.7447</v>
       </c>
       <c r="G14">
         <v>45.6</v>
@@ -2429,28 +2429,28 @@
         <v>18</v>
       </c>
       <c r="M14">
-        <v>0.26673084</v>
+        <v>0.28895841</v>
       </c>
       <c r="N14">
-        <v>17.73326916</v>
+        <v>17.71104159</v>
       </c>
       <c r="O14">
-        <v>3.546653832</v>
+        <v>3.542208318</v>
       </c>
       <c r="P14">
-        <v>14.186615328</v>
+        <v>14.168833272</v>
       </c>
       <c r="Q14">
-        <v>14.986615328</v>
+        <v>14.968833272</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1029308873716981</v>
+        <v>0.1034691470982074</v>
       </c>
       <c r="T14">
-        <v>1.083751822272144</v>
+        <v>1.093962410384752</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>67.48376003314803</v>
+        <v>62.29270156905972</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09524935797544044</v>
+        <v>0.09509073506378657</v>
       </c>
       <c r="C15">
-        <v>38.44439054365083</v>
+        <v>38.00230800537065</v>
       </c>
       <c r="D15">
-        <v>-1.410909456349174</v>
+        <v>-1.411091994629355</v>
       </c>
       <c r="E15">
-        <v>-0.4453000000000005</v>
+        <v>-0.00340000000000007</v>
       </c>
       <c r="F15">
-        <v>5.7447</v>
+        <v>6.1866</v>
       </c>
       <c r="G15">
         <v>45.6</v>
@@ -2511,28 +2511,28 @@
         <v>18</v>
       </c>
       <c r="M15">
-        <v>0.28895841</v>
+        <v>0.31118598</v>
       </c>
       <c r="N15">
-        <v>17.71104159</v>
+        <v>17.68881402</v>
       </c>
       <c r="O15">
-        <v>3.542208318</v>
+        <v>3.537762804</v>
       </c>
       <c r="P15">
-        <v>14.168833272</v>
+        <v>14.151051216</v>
       </c>
       <c r="Q15">
-        <v>14.968833272</v>
+        <v>14.951051216</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1034691470982074</v>
+        <v>0.1040199244927751</v>
       </c>
       <c r="T15">
-        <v>1.093962410384752</v>
+        <v>1.104410454034862</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>62.29270156905972</v>
+        <v>57.84322288555545</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09509073506378657</v>
+        <v>0.09493211215213268</v>
       </c>
       <c r="C16">
-        <v>38.00230800537065</v>
+        <v>37.56022541985209</v>
       </c>
       <c r="D16">
-        <v>-1.411091994629355</v>
+        <v>-1.411274580147911</v>
       </c>
       <c r="E16">
-        <v>-0.00340000000000007</v>
+        <v>0.4385000000000003</v>
       </c>
       <c r="F16">
-        <v>6.1866</v>
+        <v>6.628500000000001</v>
       </c>
       <c r="G16">
         <v>45.6</v>
@@ -2593,28 +2593,28 @@
         <v>18</v>
       </c>
       <c r="M16">
-        <v>0.31118598</v>
+        <v>0.33341355</v>
       </c>
       <c r="N16">
-        <v>17.68881402</v>
+        <v>17.66658645</v>
       </c>
       <c r="O16">
-        <v>3.537762804</v>
+        <v>3.53331729</v>
       </c>
       <c r="P16">
-        <v>14.151051216</v>
+        <v>14.13326916</v>
       </c>
       <c r="Q16">
-        <v>14.951051216</v>
+        <v>14.93326916</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1040199244927751</v>
+        <v>0.1045836613554502</v>
       </c>
       <c r="T16">
-        <v>1.104410454034862</v>
+        <v>1.11510433400615</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>57.84322288555545</v>
+        <v>53.98700802651842</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09493211215213268</v>
+        <v>0.09477348924047879</v>
       </c>
       <c r="C17">
-        <v>37.56022541985209</v>
+        <v>37.11814278707682</v>
       </c>
       <c r="D17">
-        <v>-1.411274580147911</v>
+        <v>-1.411457212923182</v>
       </c>
       <c r="E17">
-        <v>0.4384999999999994</v>
+        <v>0.880399999999999</v>
       </c>
       <c r="F17">
-        <v>6.6285</v>
+        <v>7.070399999999999</v>
       </c>
       <c r="G17">
         <v>45.6</v>
@@ -2675,28 +2675,28 @@
         <v>18</v>
       </c>
       <c r="M17">
-        <v>0.3334135499999999</v>
+        <v>0.35564112</v>
       </c>
       <c r="N17">
-        <v>17.66658645</v>
+        <v>17.64435888</v>
       </c>
       <c r="O17">
-        <v>3.53331729</v>
+        <v>3.528871776</v>
       </c>
       <c r="P17">
-        <v>14.13326916</v>
+        <v>14.115487104</v>
       </c>
       <c r="Q17">
-        <v>14.93326916</v>
+        <v>14.915487104</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1045836613554502</v>
+        <v>0.1051608205243795</v>
       </c>
       <c r="T17">
-        <v>1.11510433400615</v>
+        <v>1.126052830167232</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>53.98700802651843</v>
+        <v>50.61282002486102</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09477348924047879</v>
+        <v>0.0946148663288249</v>
       </c>
       <c r="C18">
-        <v>37.11814278707682</v>
+        <v>36.67606010702649</v>
       </c>
       <c r="D18">
-        <v>-1.411457212923182</v>
+        <v>-1.411639892973516</v>
       </c>
       <c r="E18">
-        <v>0.880399999999999</v>
+        <v>1.322299999999999</v>
       </c>
       <c r="F18">
-        <v>7.070399999999999</v>
+        <v>7.5123</v>
       </c>
       <c r="G18">
         <v>45.6</v>
@@ -2757,28 +2757,28 @@
         <v>18</v>
       </c>
       <c r="M18">
-        <v>0.35564112</v>
+        <v>0.37786869</v>
       </c>
       <c r="N18">
-        <v>17.64435888</v>
+        <v>17.62213131</v>
       </c>
       <c r="O18">
-        <v>3.528871776</v>
+        <v>3.524426262</v>
       </c>
       <c r="P18">
-        <v>14.115487104</v>
+        <v>14.097705048</v>
       </c>
       <c r="Q18">
-        <v>14.915487104</v>
+        <v>14.897705048</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1051608205243795</v>
+        <v>0.1057518871431626</v>
       </c>
       <c r="T18">
-        <v>1.126052830167232</v>
+        <v>1.137265145512918</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>50.61282002486102</v>
+        <v>47.63559531751626</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0946148663288249</v>
+        <v>0.09445624341717103</v>
       </c>
       <c r="C19">
-        <v>36.67606010702649</v>
+        <v>36.23397737968273</v>
       </c>
       <c r="D19">
-        <v>-1.411639892973516</v>
+        <v>-1.411822620317271</v>
       </c>
       <c r="E19">
-        <v>1.322299999999999</v>
+        <v>1.7642</v>
       </c>
       <c r="F19">
-        <v>7.5123</v>
+        <v>7.9542</v>
       </c>
       <c r="G19">
         <v>45.6</v>
@@ -2839,28 +2839,28 @@
         <v>18</v>
       </c>
       <c r="M19">
-        <v>0.37786869</v>
+        <v>0.40009626</v>
       </c>
       <c r="N19">
-        <v>17.62213131</v>
+        <v>17.59990374</v>
       </c>
       <c r="O19">
-        <v>3.524426262</v>
+        <v>3.519980748</v>
       </c>
       <c r="P19">
-        <v>14.097705048</v>
+        <v>14.079922992</v>
       </c>
       <c r="Q19">
-        <v>14.897705048</v>
+        <v>14.879922992</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1057518871431626</v>
+        <v>0.1063573700209403</v>
       </c>
       <c r="T19">
-        <v>1.137265145512918</v>
+        <v>1.148750931964596</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>47.63559531751626</v>
+        <v>44.98917335543202</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09445624341717104</v>
+        <v>0.09429762050551717</v>
       </c>
       <c r="C20">
-        <v>36.23397737968273</v>
+        <v>35.79189460502719</v>
       </c>
       <c r="D20">
-        <v>-1.411822620317271</v>
+        <v>-1.412005394972816</v>
       </c>
       <c r="E20">
-        <v>1.764199999999999</v>
+        <v>2.206099999999998</v>
       </c>
       <c r="F20">
-        <v>7.954199999999999</v>
+        <v>8.396099999999999</v>
       </c>
       <c r="G20">
         <v>45.6</v>
@@ -2921,28 +2921,28 @@
         <v>18</v>
       </c>
       <c r="M20">
-        <v>0.4000962599999999</v>
+        <v>0.4223238299999999</v>
       </c>
       <c r="N20">
-        <v>17.59990374</v>
+        <v>17.57767617</v>
       </c>
       <c r="O20">
-        <v>3.519980748</v>
+        <v>3.515535234</v>
       </c>
       <c r="P20">
-        <v>14.079922992</v>
+        <v>14.062140936</v>
       </c>
       <c r="Q20">
-        <v>14.879922992</v>
+        <v>14.862140936</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1063573700209403</v>
+        <v>0.1069778030932311</v>
       </c>
       <c r="T20">
-        <v>1.148750931964596</v>
+        <v>1.160520318081748</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>44.98917335543202</v>
+        <v>42.62132212619876</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09429762050551717</v>
+        <v>0.09413899759386328</v>
       </c>
       <c r="C21">
-        <v>35.79189460502719</v>
+        <v>35.34981178304147</v>
       </c>
       <c r="D21">
-        <v>-1.412005394972816</v>
+        <v>-1.412188216958528</v>
       </c>
       <c r="E21">
-        <v>2.206099999999998</v>
+        <v>2.647999999999999</v>
       </c>
       <c r="F21">
-        <v>8.396099999999999</v>
+        <v>8.837999999999999</v>
       </c>
       <c r="G21">
         <v>45.6</v>
@@ -3003,28 +3003,28 @@
         <v>18</v>
       </c>
       <c r="M21">
-        <v>0.4223238299999999</v>
+        <v>0.4445513999999999</v>
       </c>
       <c r="N21">
-        <v>17.57767617</v>
+        <v>17.5554486</v>
       </c>
       <c r="O21">
-        <v>3.515535234</v>
+        <v>3.51108972</v>
       </c>
       <c r="P21">
-        <v>14.062140936</v>
+        <v>14.04435888</v>
       </c>
       <c r="Q21">
-        <v>14.862140936</v>
+        <v>14.84435888</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1069778030932311</v>
+        <v>0.1076137469923291</v>
       </c>
       <c r="T21">
-        <v>1.160520318081748</v>
+        <v>1.172583938851828</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>42.62132212619876</v>
+        <v>40.49025601988882</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09413899759386328</v>
+        <v>0.09398037468220941</v>
       </c>
       <c r="C22">
-        <v>35.34981178304147</v>
+        <v>34.90772891370721</v>
       </c>
       <c r="D22">
-        <v>-1.412188216958528</v>
+        <v>-1.412371086292794</v>
       </c>
       <c r="E22">
-        <v>2.647999999999999</v>
+        <v>3.089899999999999</v>
       </c>
       <c r="F22">
-        <v>8.837999999999999</v>
+        <v>9.2799</v>
       </c>
       <c r="G22">
         <v>45.6</v>
@@ -3085,28 +3085,28 @@
         <v>18</v>
       </c>
       <c r="M22">
-        <v>0.4445513999999999</v>
+        <v>0.46677897</v>
       </c>
       <c r="N22">
-        <v>17.5554486</v>
+        <v>17.53322103</v>
       </c>
       <c r="O22">
-        <v>3.51108972</v>
+        <v>3.506644206</v>
       </c>
       <c r="P22">
-        <v>14.04435888</v>
+        <v>14.026576824</v>
       </c>
       <c r="Q22">
-        <v>14.84435888</v>
+        <v>14.826576824</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1076137469923291</v>
+        <v>0.1082657907369739</v>
       </c>
       <c r="T22">
-        <v>1.172583938851828</v>
+        <v>1.18495296774267</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>40.49025601988882</v>
+        <v>38.5621485903703</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09398037468220941</v>
+        <v>0.0938217517705555</v>
       </c>
       <c r="C23">
-        <v>34.90772891370721</v>
+        <v>34.46564599700599</v>
       </c>
       <c r="D23">
-        <v>-1.412371086292794</v>
+        <v>-1.412554002994009</v>
       </c>
       <c r="E23">
-        <v>3.089899999999999</v>
+        <v>3.5318</v>
       </c>
       <c r="F23">
-        <v>9.2799</v>
+        <v>9.7218</v>
       </c>
       <c r="G23">
         <v>45.6</v>
@@ -3167,28 +3167,28 @@
         <v>18</v>
       </c>
       <c r="M23">
-        <v>0.46677897</v>
+        <v>0.48900654</v>
       </c>
       <c r="N23">
-        <v>17.53322103</v>
+        <v>17.51099346</v>
       </c>
       <c r="O23">
-        <v>3.506644206</v>
+        <v>3.502198692</v>
       </c>
       <c r="P23">
-        <v>14.026576824</v>
+        <v>14.008794768</v>
       </c>
       <c r="Q23">
-        <v>14.826576824</v>
+        <v>14.808794768</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1082657907369739</v>
+        <v>0.1089345535519942</v>
       </c>
       <c r="T23">
-        <v>1.18495296774267</v>
+        <v>1.197639151220457</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>38.5621485903703</v>
+        <v>36.80932365444438</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0938217517705555</v>
+        <v>0.09366312885890164</v>
       </c>
       <c r="C24">
-        <v>34.46564599700599</v>
+        <v>34.02356303291942</v>
       </c>
       <c r="D24">
-        <v>-1.412554002994009</v>
+        <v>-1.412736967080581</v>
       </c>
       <c r="E24">
-        <v>3.5318</v>
+        <v>3.9737</v>
       </c>
       <c r="F24">
-        <v>9.7218</v>
+        <v>10.1637</v>
       </c>
       <c r="G24">
         <v>45.6</v>
@@ -3249,28 +3249,28 @@
         <v>18</v>
       </c>
       <c r="M24">
-        <v>0.48900654</v>
+        <v>0.51123411</v>
       </c>
       <c r="N24">
-        <v>17.51099346</v>
+        <v>17.48876589</v>
       </c>
       <c r="O24">
-        <v>3.502198692</v>
+        <v>3.497753178</v>
       </c>
       <c r="P24">
-        <v>14.008794768</v>
+        <v>13.991012712</v>
       </c>
       <c r="Q24">
-        <v>14.808794768</v>
+        <v>14.791012712</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1089345535519942</v>
+        <v>0.1096206868297424</v>
       </c>
       <c r="T24">
-        <v>1.197639151220457</v>
+        <v>1.210654845957407</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>36.80932365444438</v>
+        <v>35.20891827816419</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09366312885890164</v>
+        <v>0.09350450594724774</v>
       </c>
       <c r="C25">
-        <v>34.02356303291942</v>
+        <v>33.58148002142907</v>
       </c>
       <c r="D25">
-        <v>-1.412736967080581</v>
+        <v>-1.412919978570924</v>
       </c>
       <c r="E25">
-        <v>3.9737</v>
+        <v>4.4156</v>
       </c>
       <c r="F25">
-        <v>10.1637</v>
+        <v>10.6056</v>
       </c>
       <c r="G25">
         <v>45.6</v>
@@ -3331,28 +3331,28 @@
         <v>18</v>
       </c>
       <c r="M25">
-        <v>0.51123411</v>
+        <v>0.53346168</v>
       </c>
       <c r="N25">
-        <v>17.48876589</v>
+        <v>17.46653832</v>
       </c>
       <c r="O25">
-        <v>3.497753178</v>
+        <v>3.493307664</v>
       </c>
       <c r="P25">
-        <v>13.991012712</v>
+        <v>13.973230656</v>
       </c>
       <c r="Q25">
-        <v>14.791012712</v>
+        <v>14.773230656</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1096206868297424</v>
+        <v>0.1103248762463786</v>
       </c>
       <c r="T25">
-        <v>1.210654845957407</v>
+        <v>1.224013058976908</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>35.20891827816419</v>
+        <v>33.74188001657401</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09350450594724774</v>
+        <v>0.09334588303559387</v>
       </c>
       <c r="C26">
-        <v>33.58148002142907</v>
+        <v>33.13939696251654</v>
       </c>
       <c r="D26">
-        <v>-1.412919978570924</v>
+        <v>-1.413103037483464</v>
       </c>
       <c r="E26">
-        <v>4.415599999999999</v>
+        <v>4.857499999999999</v>
       </c>
       <c r="F26">
-        <v>10.6056</v>
+        <v>11.0475</v>
       </c>
       <c r="G26">
         <v>45.6</v>
@@ -3413,28 +3413,28 @@
         <v>18</v>
       </c>
       <c r="M26">
-        <v>0.5334616799999999</v>
+        <v>0.5556892499999999</v>
       </c>
       <c r="N26">
-        <v>17.46653832</v>
+        <v>17.44431075</v>
       </c>
       <c r="O26">
-        <v>3.493307664</v>
+        <v>3.48886215</v>
       </c>
       <c r="P26">
-        <v>13.973230656</v>
+        <v>13.9554486</v>
       </c>
       <c r="Q26">
-        <v>14.773230656</v>
+        <v>14.7554486</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1103248762463786</v>
+        <v>0.1110478440474585</v>
       </c>
       <c r="T26">
-        <v>1.224013058976908</v>
+        <v>1.237727491010263</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>33.74188001657402</v>
+        <v>32.39220481591106</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09334588303559387</v>
+        <v>0.09318726012393998</v>
       </c>
       <c r="C27">
-        <v>33.13939696251654</v>
+        <v>32.69731385616336</v>
       </c>
       <c r="D27">
-        <v>-1.413103037483464</v>
+        <v>-1.413286143836634</v>
       </c>
       <c r="E27">
-        <v>4.857499999999999</v>
+        <v>5.299399999999999</v>
       </c>
       <c r="F27">
-        <v>11.0475</v>
+        <v>11.4894</v>
       </c>
       <c r="G27">
         <v>45.6</v>
@@ -3495,28 +3495,28 @@
         <v>18</v>
       </c>
       <c r="M27">
-        <v>0.5556892499999999</v>
+        <v>0.57791682</v>
       </c>
       <c r="N27">
-        <v>17.44431075</v>
+        <v>17.42208318</v>
       </c>
       <c r="O27">
-        <v>3.48886215</v>
+        <v>3.484416636000001</v>
       </c>
       <c r="P27">
-        <v>13.9554486</v>
+        <v>13.937666544</v>
       </c>
       <c r="Q27">
-        <v>14.7554486</v>
+        <v>14.737666544</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1110478440474585</v>
+        <v>0.1117903515188378</v>
       </c>
       <c r="T27">
-        <v>1.237727491010263</v>
+        <v>1.251812583368844</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>32.39220481591106</v>
+        <v>31.14635078452986</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09318726012393998</v>
+        <v>0.0930286372122861</v>
       </c>
       <c r="C28">
-        <v>32.69731385616336</v>
+        <v>32.25523070235112</v>
       </c>
       <c r="D28">
-        <v>-1.413286143836634</v>
+        <v>-1.41346929764888</v>
       </c>
       <c r="E28">
-        <v>5.299399999999999</v>
+        <v>5.7413</v>
       </c>
       <c r="F28">
-        <v>11.4894</v>
+        <v>11.9313</v>
       </c>
       <c r="G28">
         <v>45.6</v>
@@ -3577,28 +3577,28 @@
         <v>18</v>
       </c>
       <c r="M28">
-        <v>0.57791682</v>
+        <v>0.60014439</v>
       </c>
       <c r="N28">
-        <v>17.42208318</v>
+        <v>17.39985561</v>
       </c>
       <c r="O28">
-        <v>3.484416636000001</v>
+        <v>3.479971122</v>
       </c>
       <c r="P28">
-        <v>13.937666544</v>
+        <v>13.919884488</v>
       </c>
       <c r="Q28">
-        <v>14.737666544</v>
+        <v>14.719884488</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1117903515188378</v>
+        <v>0.1125532016606659</v>
       </c>
       <c r="T28">
-        <v>1.251812583368844</v>
+        <v>1.266283568668755</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>31.14635078452986</v>
+        <v>29.99278223695468</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0930286372122861</v>
+        <v>0.09287001430063223</v>
       </c>
       <c r="C29">
-        <v>32.25523070235112</v>
+        <v>31.81314750106135</v>
       </c>
       <c r="D29">
-        <v>-1.41346929764888</v>
+        <v>-1.413652498938654</v>
       </c>
       <c r="E29">
-        <v>5.7413</v>
+        <v>6.1832</v>
       </c>
       <c r="F29">
-        <v>11.9313</v>
+        <v>12.3732</v>
       </c>
       <c r="G29">
         <v>45.6</v>
@@ -3659,28 +3659,28 @@
         <v>18</v>
       </c>
       <c r="M29">
-        <v>0.60014439</v>
+        <v>0.6223719599999999</v>
       </c>
       <c r="N29">
-        <v>17.39985561</v>
+        <v>17.37762804</v>
       </c>
       <c r="O29">
-        <v>3.479971122</v>
+        <v>3.475525608</v>
       </c>
       <c r="P29">
-        <v>13.919884488</v>
+        <v>13.902102432</v>
       </c>
       <c r="Q29">
-        <v>14.719884488</v>
+        <v>14.702102432</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1125532016606659</v>
+        <v>0.1133372420842114</v>
       </c>
       <c r="T29">
-        <v>1.266283568668755</v>
+        <v>1.281156525782553</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>29.99278223695468</v>
+        <v>28.92161144277773</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09287001430063223</v>
+        <v>0.09271139138897835</v>
       </c>
       <c r="C30">
-        <v>31.81314750106135</v>
+        <v>31.37106425227558</v>
       </c>
       <c r="D30">
-        <v>-1.413652498938654</v>
+        <v>-1.413835747724421</v>
       </c>
       <c r="E30">
-        <v>6.1832</v>
+        <v>6.625100000000001</v>
       </c>
       <c r="F30">
-        <v>12.3732</v>
+        <v>12.8151</v>
       </c>
       <c r="G30">
         <v>45.6</v>
@@ -3741,28 +3741,28 @@
         <v>18</v>
       </c>
       <c r="M30">
-        <v>0.6223719599999999</v>
+        <v>0.64459953</v>
       </c>
       <c r="N30">
-        <v>17.37762804</v>
+        <v>17.35540047</v>
       </c>
       <c r="O30">
-        <v>3.475525608</v>
+        <v>3.471080094</v>
       </c>
       <c r="P30">
-        <v>13.902102432</v>
+        <v>13.884320376</v>
       </c>
       <c r="Q30">
-        <v>14.702102432</v>
+        <v>14.684320376</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1133372420842114</v>
+        <v>0.1141433681534906</v>
       </c>
       <c r="T30">
-        <v>1.281156525782553</v>
+        <v>1.296448439434768</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>28.92161144277773</v>
+        <v>27.92431449647504</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09271139138897835</v>
+        <v>0.09255276847732445</v>
       </c>
       <c r="C31">
-        <v>31.37106425227558</v>
+        <v>30.92898095597535</v>
       </c>
       <c r="D31">
-        <v>-1.413835747724421</v>
+        <v>-1.414019044024652</v>
       </c>
       <c r="E31">
-        <v>6.625099999999999</v>
+        <v>7.066999999999999</v>
       </c>
       <c r="F31">
-        <v>12.8151</v>
+        <v>13.257</v>
       </c>
       <c r="G31">
         <v>45.6</v>
@@ -3823,28 +3823,28 @@
         <v>18</v>
       </c>
       <c r="M31">
-        <v>0.6445995299999999</v>
+        <v>0.6668270999999999</v>
       </c>
       <c r="N31">
-        <v>17.35540047</v>
+        <v>17.3331729</v>
       </c>
       <c r="O31">
-        <v>3.471080094</v>
+        <v>3.46663458</v>
       </c>
       <c r="P31">
-        <v>13.884320376</v>
+        <v>13.86653832</v>
       </c>
       <c r="Q31">
-        <v>14.684320376</v>
+        <v>14.66653832</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1141433681534906</v>
+        <v>0.1149725263961778</v>
       </c>
       <c r="T31">
-        <v>1.296448439434768</v>
+        <v>1.312177264905617</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>27.92431449647504</v>
+        <v>26.99350401325922</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09255276847732445</v>
+        <v>0.09239414556567055</v>
       </c>
       <c r="C32">
-        <v>30.92898095597535</v>
+        <v>30.48689761214217</v>
       </c>
       <c r="D32">
-        <v>-1.414019044024652</v>
+        <v>-1.414202387857831</v>
       </c>
       <c r="E32">
-        <v>7.066999999999999</v>
+        <v>7.5089</v>
       </c>
       <c r="F32">
-        <v>13.257</v>
+        <v>13.6989</v>
       </c>
       <c r="G32">
         <v>45.6</v>
@@ -3905,28 +3905,28 @@
         <v>18</v>
       </c>
       <c r="M32">
-        <v>0.6668270999999999</v>
+        <v>0.68905467</v>
       </c>
       <c r="N32">
-        <v>17.3331729</v>
+        <v>17.31094533</v>
       </c>
       <c r="O32">
-        <v>3.46663458</v>
+        <v>3.462189066</v>
       </c>
       <c r="P32">
-        <v>13.86653832</v>
+        <v>13.848756264</v>
       </c>
       <c r="Q32">
-        <v>14.66653832</v>
+        <v>14.648756264</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1149725263961778</v>
+        <v>0.1158257182111168</v>
       </c>
       <c r="T32">
-        <v>1.312177264905617</v>
+        <v>1.328361998361129</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>26.99350401325922</v>
+        <v>26.1227458192831</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09239414556567055</v>
+        <v>0.09223552265401669</v>
       </c>
       <c r="C33">
-        <v>30.48689761214217</v>
+        <v>30.04481422075755</v>
       </c>
       <c r="D33">
-        <v>-1.414202387857831</v>
+        <v>-1.414385779242449</v>
       </c>
       <c r="E33">
-        <v>7.5089</v>
+        <v>7.950799999999998</v>
       </c>
       <c r="F33">
-        <v>13.6989</v>
+        <v>14.1408</v>
       </c>
       <c r="G33">
         <v>45.6</v>
@@ -3987,28 +3987,28 @@
         <v>18</v>
       </c>
       <c r="M33">
-        <v>0.68905467</v>
+        <v>0.71128224</v>
       </c>
       <c r="N33">
-        <v>17.31094533</v>
+        <v>17.28871776</v>
       </c>
       <c r="O33">
-        <v>3.462189066</v>
+        <v>3.457743552</v>
       </c>
       <c r="P33">
-        <v>13.848756264</v>
+        <v>13.830974208</v>
       </c>
       <c r="Q33">
-        <v>14.648756264</v>
+        <v>14.630974208</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1158257182111168</v>
+        <v>0.1167040039029657</v>
       </c>
       <c r="T33">
-        <v>1.328361998361129</v>
+        <v>1.345022753388862</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>26.1227458192831</v>
+        <v>25.30641001243051</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09223552265401669</v>
+        <v>0.09207689974236281</v>
       </c>
       <c r="C34">
-        <v>30.04481422075755</v>
+        <v>29.60273078180299</v>
       </c>
       <c r="D34">
-        <v>-1.414385779242449</v>
+        <v>-1.414569218197007</v>
       </c>
       <c r="E34">
-        <v>7.950799999999998</v>
+        <v>8.392699999999998</v>
       </c>
       <c r="F34">
-        <v>14.1408</v>
+        <v>14.5827</v>
       </c>
       <c r="G34">
         <v>45.6</v>
@@ -4069,28 +4069,28 @@
         <v>18</v>
       </c>
       <c r="M34">
-        <v>0.71128224</v>
+        <v>0.7335098099999999</v>
       </c>
       <c r="N34">
-        <v>17.28871776</v>
+        <v>17.26649019</v>
       </c>
       <c r="O34">
-        <v>3.457743552</v>
+        <v>3.453298038</v>
       </c>
       <c r="P34">
-        <v>13.830974208</v>
+        <v>13.813192152</v>
       </c>
       <c r="Q34">
-        <v>14.630974208</v>
+        <v>14.613192152</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1167040039029657</v>
+        <v>0.1176085070781535</v>
       </c>
       <c r="T34">
-        <v>1.345022753388862</v>
+        <v>1.362180844387572</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>25.30641001243051</v>
+        <v>24.53954910296292</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09207689974236281</v>
+        <v>0.09191827683070891</v>
       </c>
       <c r="C35">
-        <v>29.60273078180299</v>
+        <v>29.16064729525998</v>
       </c>
       <c r="D35">
-        <v>-1.414569218197007</v>
+        <v>-1.414752704740017</v>
       </c>
       <c r="E35">
-        <v>8.392699999999998</v>
+        <v>8.834599999999998</v>
       </c>
       <c r="F35">
-        <v>14.5827</v>
+        <v>15.0246</v>
       </c>
       <c r="G35">
         <v>45.6</v>
@@ -4151,28 +4151,28 @@
         <v>18</v>
       </c>
       <c r="M35">
-        <v>0.7335098099999999</v>
+        <v>0.7557373799999999</v>
       </c>
       <c r="N35">
-        <v>17.26649019</v>
+        <v>17.24426262</v>
       </c>
       <c r="O35">
-        <v>3.453298038</v>
+        <v>3.448852524</v>
       </c>
       <c r="P35">
-        <v>13.813192152</v>
+        <v>13.795410096</v>
       </c>
       <c r="Q35">
-        <v>14.613192152</v>
+        <v>14.595410096</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1176085070781535</v>
+        <v>0.1185404194404681</v>
       </c>
       <c r="T35">
-        <v>1.362180844387572</v>
+        <v>1.379858877537757</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>24.53954910296292</v>
+        <v>23.81779765875813</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09191827683070891</v>
+        <v>0.09175965391905504</v>
       </c>
       <c r="C36">
-        <v>29.16064729525998</v>
+        <v>28.71856376111</v>
       </c>
       <c r="D36">
-        <v>-1.414752704740017</v>
+        <v>-1.414936238890001</v>
       </c>
       <c r="E36">
-        <v>8.834599999999998</v>
+        <v>9.276499999999999</v>
       </c>
       <c r="F36">
-        <v>15.0246</v>
+        <v>15.4665</v>
       </c>
       <c r="G36">
         <v>45.6</v>
@@ -4233,28 +4233,28 @@
         <v>18</v>
       </c>
       <c r="M36">
-        <v>0.7557373799999999</v>
+        <v>0.77796495</v>
       </c>
       <c r="N36">
-        <v>17.24426262</v>
+        <v>17.22203505</v>
       </c>
       <c r="O36">
-        <v>3.448852524</v>
+        <v>3.44440701</v>
       </c>
       <c r="P36">
-        <v>13.795410096</v>
+        <v>13.77762804</v>
       </c>
       <c r="Q36">
-        <v>14.595410096</v>
+        <v>14.57762804</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1185404194404681</v>
+        <v>0.1195010060293155</v>
       </c>
       <c r="T36">
-        <v>1.379858877537757</v>
+        <v>1.398080850169487</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>23.81779765875813</v>
+        <v>23.13728915422218</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09175965391905504</v>
+        <v>0.09160103100740115</v>
       </c>
       <c r="C37">
-        <v>28.71856376111</v>
+        <v>28.27648017933451</v>
       </c>
       <c r="D37">
-        <v>-1.414936238890001</v>
+        <v>-1.415119820665487</v>
       </c>
       <c r="E37">
-        <v>9.276499999999999</v>
+        <v>9.718399999999999</v>
       </c>
       <c r="F37">
-        <v>15.4665</v>
+        <v>15.9084</v>
       </c>
       <c r="G37">
         <v>45.6</v>
@@ -4315,28 +4315,28 @@
         <v>18</v>
       </c>
       <c r="M37">
-        <v>0.77796495</v>
+        <v>0.80019252</v>
       </c>
       <c r="N37">
-        <v>17.22203505</v>
+        <v>17.19980748</v>
       </c>
       <c r="O37">
-        <v>3.44440701</v>
+        <v>3.439961496</v>
       </c>
       <c r="P37">
-        <v>13.77762804</v>
+        <v>13.759845984</v>
       </c>
       <c r="Q37">
-        <v>14.57762804</v>
+        <v>14.559845984</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1195010060293155</v>
+        <v>0.1204916109490643</v>
       </c>
       <c r="T37">
-        <v>1.398080850169487</v>
+        <v>1.416872259445959</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>23.13728915422218</v>
+        <v>22.49458667771601</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09160103100740116</v>
+        <v>0.09144240809574729</v>
       </c>
       <c r="C38">
-        <v>28.27648017933451</v>
+        <v>27.83439654991498</v>
       </c>
       <c r="D38">
-        <v>-1.415119820665487</v>
+        <v>-1.415303450085017</v>
       </c>
       <c r="E38">
-        <v>9.718399999999999</v>
+        <v>10.1603</v>
       </c>
       <c r="F38">
-        <v>15.9084</v>
+        <v>16.3503</v>
       </c>
       <c r="G38">
         <v>45.6</v>
@@ -4397,28 +4397,28 @@
         <v>18</v>
       </c>
       <c r="M38">
-        <v>0.8001925199999999</v>
+        <v>0.82242009</v>
       </c>
       <c r="N38">
-        <v>17.19980748</v>
+        <v>17.17757991</v>
       </c>
       <c r="O38">
-        <v>3.439961496</v>
+        <v>3.435515982</v>
       </c>
       <c r="P38">
-        <v>13.759845984</v>
+        <v>13.742063928</v>
       </c>
       <c r="Q38">
-        <v>14.559845984</v>
+        <v>14.542063928</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1204916109490643</v>
+        <v>0.1215136636440433</v>
       </c>
       <c r="T38">
-        <v>1.416872259445959</v>
+        <v>1.436260221397874</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>22.49458667771601</v>
+        <v>21.88662487561557</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09144240809574729</v>
+        <v>0.0912837851840934</v>
       </c>
       <c r="C39">
-        <v>27.83439654991498</v>
+        <v>27.39231287283286</v>
       </c>
       <c r="D39">
-        <v>-1.415303450085017</v>
+        <v>-1.415487127167139</v>
       </c>
       <c r="E39">
-        <v>10.1603</v>
+        <v>10.6022</v>
       </c>
       <c r="F39">
-        <v>16.3503</v>
+        <v>16.7922</v>
       </c>
       <c r="G39">
         <v>45.6</v>
@@ -4479,28 +4479,28 @@
         <v>18</v>
       </c>
       <c r="M39">
-        <v>0.82242009</v>
+        <v>0.8446476599999998</v>
       </c>
       <c r="N39">
-        <v>17.17757991</v>
+        <v>17.15535234</v>
       </c>
       <c r="O39">
-        <v>3.435515982</v>
+        <v>3.431070468</v>
       </c>
       <c r="P39">
-        <v>13.742063928</v>
+        <v>13.724281872</v>
       </c>
       <c r="Q39">
-        <v>14.542063928</v>
+        <v>14.524281872</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1215136636440433</v>
+        <v>0.1225686857807958</v>
       </c>
       <c r="T39">
-        <v>1.436260221397874</v>
+        <v>1.456273601477271</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>21.88662487561557</v>
+        <v>21.31066106309938</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0912837851840934</v>
+        <v>0.09112516227243952</v>
       </c>
       <c r="C40">
-        <v>27.39231287283286</v>
+        <v>26.95022914806959</v>
       </c>
       <c r="D40">
-        <v>-1.415487127167139</v>
+        <v>-1.415670851930413</v>
       </c>
       <c r="E40">
-        <v>10.6022</v>
+        <v>11.0441</v>
       </c>
       <c r="F40">
-        <v>16.7922</v>
+        <v>17.2341</v>
       </c>
       <c r="G40">
         <v>45.6</v>
@@ -4561,28 +4561,28 @@
         <v>18</v>
       </c>
       <c r="M40">
-        <v>0.8446476599999998</v>
+        <v>0.8668752299999999</v>
       </c>
       <c r="N40">
-        <v>17.15535234</v>
+        <v>17.13312477</v>
       </c>
       <c r="O40">
-        <v>3.431070468</v>
+        <v>3.426624954</v>
       </c>
       <c r="P40">
-        <v>13.724281872</v>
+        <v>13.706499816</v>
       </c>
       <c r="Q40">
-        <v>14.524281872</v>
+        <v>14.506499816</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1225686857807958</v>
+        <v>0.1236582988072779</v>
       </c>
       <c r="T40">
-        <v>1.456273601477271</v>
+        <v>1.476943157952713</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>21.31066106309938</v>
+        <v>20.76423385635324</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09112516227243952</v>
+        <v>0.09096653936078562</v>
       </c>
       <c r="C41">
-        <v>26.95022914806959</v>
+        <v>26.50814537560659</v>
       </c>
       <c r="D41">
-        <v>-1.415670851930413</v>
+        <v>-1.415854624393408</v>
       </c>
       <c r="E41">
-        <v>11.0441</v>
+        <v>11.486</v>
       </c>
       <c r="F41">
-        <v>17.2341</v>
+        <v>17.676</v>
       </c>
       <c r="G41">
         <v>45.6</v>
@@ -4643,28 +4643,28 @@
         <v>18</v>
       </c>
       <c r="M41">
-        <v>0.8668752299999999</v>
+        <v>0.8891027999999999</v>
       </c>
       <c r="N41">
-        <v>17.13312477</v>
+        <v>17.1108972</v>
       </c>
       <c r="O41">
-        <v>3.426624954</v>
+        <v>3.42217944</v>
       </c>
       <c r="P41">
-        <v>13.706499816</v>
+        <v>13.68871776</v>
       </c>
       <c r="Q41">
-        <v>14.506499816</v>
+        <v>14.48871776</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1236582988072779</v>
+        <v>0.1247842322679761</v>
       </c>
       <c r="T41">
-        <v>1.476943157952713</v>
+        <v>1.498301699644003</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>20.76423385635324</v>
+        <v>20.24512800994441</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09096653936078562</v>
+        <v>0.09080791644913175</v>
       </c>
       <c r="C42">
-        <v>26.50814537560659</v>
+        <v>26.0660615554253</v>
       </c>
       <c r="D42">
-        <v>-1.415854624393408</v>
+        <v>-1.416038444574702</v>
       </c>
       <c r="E42">
-        <v>11.486</v>
+        <v>11.9279</v>
       </c>
       <c r="F42">
-        <v>17.676</v>
+        <v>18.1179</v>
       </c>
       <c r="G42">
         <v>45.6</v>
@@ -4725,28 +4725,28 @@
         <v>18</v>
       </c>
       <c r="M42">
-        <v>0.8891027999999999</v>
+        <v>0.9113303699999999</v>
       </c>
       <c r="N42">
-        <v>17.1108972</v>
+        <v>17.08866963</v>
       </c>
       <c r="O42">
-        <v>3.42217944</v>
+        <v>3.417733926</v>
       </c>
       <c r="P42">
-        <v>13.68871776</v>
+        <v>13.670935704</v>
       </c>
       <c r="Q42">
-        <v>14.48871776</v>
+        <v>14.470935704</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1247842322679761</v>
+        <v>0.1259483329646301</v>
       </c>
       <c r="T42">
-        <v>1.498301699644003</v>
+        <v>1.52038425969771</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>20.24512800994441</v>
+        <v>19.75134439994576</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09080791644913175</v>
+        <v>0.09064929353747786</v>
       </c>
       <c r="C43">
-        <v>26.0660615554253</v>
+        <v>25.62397768750712</v>
       </c>
       <c r="D43">
-        <v>-1.416038444574702</v>
+        <v>-1.416222312492884</v>
       </c>
       <c r="E43">
-        <v>11.9279</v>
+        <v>12.3698</v>
       </c>
       <c r="F43">
-        <v>18.1179</v>
+        <v>18.5598</v>
       </c>
       <c r="G43">
         <v>45.6</v>
@@ -4807,28 +4807,28 @@
         <v>18</v>
       </c>
       <c r="M43">
-        <v>0.9113303699999999</v>
+        <v>0.9335579399999999</v>
       </c>
       <c r="N43">
-        <v>17.08866963</v>
+        <v>17.06644206</v>
       </c>
       <c r="O43">
-        <v>3.417733926</v>
+        <v>3.413288412</v>
       </c>
       <c r="P43">
-        <v>13.670935704</v>
+        <v>13.653153648</v>
       </c>
       <c r="Q43">
-        <v>14.470935704</v>
+        <v>14.453153648</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1259483329646301</v>
+        <v>0.127152575064617</v>
       </c>
       <c r="T43">
-        <v>1.52038425969771</v>
+        <v>1.543228287339475</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>19.75134439994576</v>
+        <v>19.28107429518515</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09064929353747787</v>
+        <v>0.090490670625824</v>
       </c>
       <c r="C44">
-        <v>25.62397768750712</v>
+        <v>25.18189377183345</v>
       </c>
       <c r="D44">
-        <v>-1.416222312492884</v>
+        <v>-1.416406228166552</v>
       </c>
       <c r="E44">
-        <v>12.3698</v>
+        <v>12.8117</v>
       </c>
       <c r="F44">
-        <v>18.5598</v>
+        <v>19.0017</v>
       </c>
       <c r="G44">
         <v>45.6</v>
@@ -4889,28 +4889,28 @@
         <v>18</v>
       </c>
       <c r="M44">
-        <v>0.9335579399999999</v>
+        <v>0.9557855099999999</v>
       </c>
       <c r="N44">
-        <v>17.06644206</v>
+        <v>17.04421449</v>
       </c>
       <c r="O44">
-        <v>3.413288412</v>
+        <v>3.408842898000001</v>
       </c>
       <c r="P44">
-        <v>13.653153648</v>
+        <v>13.635371592</v>
       </c>
       <c r="Q44">
-        <v>14.453153648</v>
+        <v>14.435371592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.127152575064617</v>
+        <v>0.1283990712733754</v>
       </c>
       <c r="T44">
-        <v>1.543228287339475</v>
+        <v>1.566873859810777</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>19.28107429518515</v>
+        <v>18.83267721855294</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.090490670625824</v>
+        <v>0.09033204771417012</v>
       </c>
       <c r="C45">
-        <v>25.18189377183345</v>
+        <v>24.73980980838569</v>
       </c>
       <c r="D45">
-        <v>-1.416406228166552</v>
+        <v>-1.416590191614312</v>
       </c>
       <c r="E45">
-        <v>12.8117</v>
+        <v>13.2536</v>
       </c>
       <c r="F45">
-        <v>19.0017</v>
+        <v>19.4436</v>
       </c>
       <c r="G45">
         <v>45.6</v>
@@ -4971,28 +4971,28 @@
         <v>18</v>
       </c>
       <c r="M45">
-        <v>0.9557855099999999</v>
+        <v>0.97801308</v>
       </c>
       <c r="N45">
-        <v>17.04421449</v>
+        <v>17.02198692</v>
       </c>
       <c r="O45">
-        <v>3.408842898000001</v>
+        <v>3.404397384</v>
       </c>
       <c r="P45">
-        <v>13.635371592</v>
+        <v>13.617589536</v>
       </c>
       <c r="Q45">
-        <v>14.435371592</v>
+        <v>14.417589536</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1283990712733754</v>
+        <v>0.1296900852038752</v>
       </c>
       <c r="T45">
-        <v>1.566873859810777</v>
+        <v>1.591363917013195</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>18.83267721855294</v>
+        <v>18.40466182722219</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09033204771417012</v>
+        <v>0.09017342480251624</v>
       </c>
       <c r="C46">
-        <v>24.73980980838569</v>
+        <v>24.29772579714522</v>
       </c>
       <c r="D46">
-        <v>-1.416590191614312</v>
+        <v>-1.416774202854783</v>
       </c>
       <c r="E46">
-        <v>13.2536</v>
+        <v>13.6955</v>
       </c>
       <c r="F46">
-        <v>19.4436</v>
+        <v>19.8855</v>
       </c>
       <c r="G46">
         <v>45.6</v>
@@ -5053,28 +5053,28 @@
         <v>18</v>
       </c>
       <c r="M46">
-        <v>0.97801308</v>
+        <v>1.00024065</v>
       </c>
       <c r="N46">
-        <v>17.02198692</v>
+        <v>16.99975935</v>
       </c>
       <c r="O46">
-        <v>3.404397384</v>
+        <v>3.399951870000001</v>
       </c>
       <c r="P46">
-        <v>13.617589536</v>
+        <v>13.59980748</v>
       </c>
       <c r="Q46">
-        <v>14.417589536</v>
+        <v>14.39980748</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1296900852038752</v>
+        <v>0.131028045095484</v>
       </c>
       <c r="T46">
-        <v>1.591363917013195</v>
+        <v>1.616744521750248</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>18.40466182722219</v>
+        <v>17.99566934217281</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09017342480251624</v>
+        <v>0.09001480189086235</v>
       </c>
       <c r="C47">
-        <v>24.29772579714522</v>
+        <v>23.85564173809341</v>
       </c>
       <c r="D47">
-        <v>-1.416774202854783</v>
+        <v>-1.416958261906591</v>
       </c>
       <c r="E47">
-        <v>13.6955</v>
+        <v>14.1374</v>
       </c>
       <c r="F47">
-        <v>19.8855</v>
+        <v>20.3274</v>
       </c>
       <c r="G47">
         <v>45.6</v>
@@ -5135,28 +5135,28 @@
         <v>18</v>
       </c>
       <c r="M47">
-        <v>1.00024065</v>
+        <v>1.02246822</v>
       </c>
       <c r="N47">
-        <v>16.99975935</v>
+        <v>16.97753178</v>
       </c>
       <c r="O47">
-        <v>3.399951870000001</v>
+        <v>3.395506356</v>
       </c>
       <c r="P47">
-        <v>13.59980748</v>
+        <v>13.582025424</v>
       </c>
       <c r="Q47">
-        <v>14.39980748</v>
+        <v>14.382025424</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.131028045095484</v>
+        <v>0.1324155590571525</v>
       </c>
       <c r="T47">
-        <v>1.616744521750248</v>
+        <v>1.643065148884969</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>17.99566934217281</v>
+        <v>17.6044591390821</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09001480189086235</v>
+        <v>0.08985617897920847</v>
       </c>
       <c r="C48">
-        <v>23.85564173809341</v>
+        <v>23.41355763121163</v>
       </c>
       <c r="D48">
-        <v>-1.416958261906591</v>
+        <v>-1.417142368788372</v>
       </c>
       <c r="E48">
-        <v>14.1374</v>
+        <v>14.5793</v>
       </c>
       <c r="F48">
-        <v>20.3274</v>
+        <v>20.7693</v>
       </c>
       <c r="G48">
         <v>45.6</v>
@@ -5217,28 +5217,28 @@
         <v>18</v>
       </c>
       <c r="M48">
-        <v>1.02246822</v>
+        <v>1.04469579</v>
       </c>
       <c r="N48">
-        <v>16.97753178</v>
+        <v>16.95530421</v>
       </c>
       <c r="O48">
-        <v>3.395506356</v>
+        <v>3.391060842</v>
       </c>
       <c r="P48">
-        <v>13.582025424</v>
+        <v>13.564243368</v>
       </c>
       <c r="Q48">
-        <v>14.382025424</v>
+        <v>14.364243368</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1324155590571525</v>
+        <v>0.1338554320362424</v>
       </c>
       <c r="T48">
-        <v>1.643065148884969</v>
+        <v>1.670379007232321</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>17.6044591390821</v>
+        <v>17.22989617867609</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08985617897920847</v>
+        <v>0.08969755606755458</v>
       </c>
       <c r="C49">
-        <v>23.41355763121163</v>
+        <v>22.97147347648123</v>
       </c>
       <c r="D49">
-        <v>-1.417142368788372</v>
+        <v>-1.417326523518773</v>
       </c>
       <c r="E49">
-        <v>14.5793</v>
+        <v>15.0212</v>
       </c>
       <c r="F49">
-        <v>20.7693</v>
+        <v>21.2112</v>
       </c>
       <c r="G49">
         <v>45.6</v>
@@ -5299,28 +5299,28 @@
         <v>18</v>
       </c>
       <c r="M49">
-        <v>1.04469579</v>
+        <v>1.06692336</v>
       </c>
       <c r="N49">
-        <v>16.95530421</v>
+        <v>16.93307664</v>
       </c>
       <c r="O49">
-        <v>3.391060842</v>
+        <v>3.386615328</v>
       </c>
       <c r="P49">
-        <v>13.564243368</v>
+        <v>13.546461312</v>
       </c>
       <c r="Q49">
-        <v>14.364243368</v>
+        <v>14.346461312</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1338554320362424</v>
+        <v>0.1353506847452973</v>
       </c>
       <c r="T49">
-        <v>1.670379007232321</v>
+        <v>1.698743398593033</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>17.22989617867609</v>
+        <v>16.870940008287</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08969755606755458</v>
+        <v>0.0895389331559007</v>
       </c>
       <c r="C50">
-        <v>22.97147347648123</v>
+        <v>22.52938927388356</v>
       </c>
       <c r="D50">
-        <v>-1.417326523518773</v>
+        <v>-1.41751072611645</v>
       </c>
       <c r="E50">
-        <v>15.0212</v>
+        <v>15.4631</v>
       </c>
       <c r="F50">
-        <v>21.2112</v>
+        <v>21.6531</v>
       </c>
       <c r="G50">
         <v>45.6</v>
@@ -5381,28 +5381,28 @@
         <v>18</v>
       </c>
       <c r="M50">
-        <v>1.06692336</v>
+        <v>1.08915093</v>
       </c>
       <c r="N50">
-        <v>16.93307664</v>
+        <v>16.91084907</v>
       </c>
       <c r="O50">
-        <v>3.386615328</v>
+        <v>3.382169814</v>
       </c>
       <c r="P50">
-        <v>13.546461312</v>
+        <v>13.528679256</v>
       </c>
       <c r="Q50">
-        <v>14.346461312</v>
+        <v>14.328679256</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1353506847452973</v>
+        <v>0.1369045748154916</v>
       </c>
       <c r="T50">
-        <v>1.698743398593033</v>
+        <v>1.728220119026714</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>16.87094000828701</v>
+        <v>16.5266351101587</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0895389331559007</v>
+        <v>0.08938031024424681</v>
       </c>
       <c r="C51">
-        <v>22.52938927388356</v>
+        <v>22.08730502339994</v>
       </c>
       <c r="D51">
-        <v>-1.41751072611645</v>
+        <v>-1.417694976600068</v>
       </c>
       <c r="E51">
-        <v>15.4631</v>
+        <v>15.905</v>
       </c>
       <c r="F51">
-        <v>21.6531</v>
+        <v>22.095</v>
       </c>
       <c r="G51">
         <v>45.6</v>
@@ -5463,28 +5463,28 @@
         <v>18</v>
       </c>
       <c r="M51">
-        <v>1.08915093</v>
+        <v>1.1113785</v>
       </c>
       <c r="N51">
-        <v>16.91084907</v>
+        <v>16.8886215</v>
       </c>
       <c r="O51">
-        <v>3.382169814</v>
+        <v>3.3777243</v>
       </c>
       <c r="P51">
-        <v>13.528679256</v>
+        <v>13.5108972</v>
       </c>
       <c r="Q51">
-        <v>14.328679256</v>
+        <v>14.3108972</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1369045748154916</v>
+        <v>0.1385206204884936</v>
       </c>
       <c r="T51">
-        <v>1.728220119026714</v>
+        <v>1.758875908277742</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>16.5266351101587</v>
+        <v>16.19610240795553</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08938031024424681</v>
+        <v>0.08922168733259293</v>
       </c>
       <c r="C52">
-        <v>22.08730502339994</v>
+        <v>21.6452207250117</v>
       </c>
       <c r="D52">
-        <v>-1.417694976600068</v>
+        <v>-1.417879274988302</v>
       </c>
       <c r="E52">
-        <v>15.905</v>
+        <v>16.3469</v>
       </c>
       <c r="F52">
-        <v>22.095</v>
+        <v>22.5369</v>
       </c>
       <c r="G52">
         <v>45.6</v>
@@ -5545,28 +5545,28 @@
         <v>18</v>
       </c>
       <c r="M52">
-        <v>1.1113785</v>
+        <v>1.13360607</v>
       </c>
       <c r="N52">
-        <v>16.8886215</v>
+        <v>16.86639393</v>
       </c>
       <c r="O52">
-        <v>3.3777243</v>
+        <v>3.373278786</v>
       </c>
       <c r="P52">
-        <v>13.5108972</v>
+        <v>13.493115144</v>
       </c>
       <c r="Q52">
-        <v>14.3108972</v>
+        <v>14.293115144</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1385206204884936</v>
+        <v>0.1402026272093733</v>
       </c>
       <c r="T52">
-        <v>1.758875908277742</v>
+        <v>1.790782954232894</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>16.19610240795553</v>
+        <v>15.87853177250542</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08922168733259293</v>
+        <v>0.08906306442093906</v>
       </c>
       <c r="C53">
-        <v>21.6452207250117</v>
+        <v>21.20313637870017</v>
       </c>
       <c r="D53">
-        <v>-1.417879274988302</v>
+        <v>-1.418063621299839</v>
       </c>
       <c r="E53">
-        <v>16.3469</v>
+        <v>16.7888</v>
       </c>
       <c r="F53">
-        <v>22.5369</v>
+        <v>22.9788</v>
       </c>
       <c r="G53">
         <v>45.6</v>
@@ -5627,28 +5627,28 @@
         <v>18</v>
       </c>
       <c r="M53">
-        <v>1.13360607</v>
+        <v>1.15583364</v>
       </c>
       <c r="N53">
-        <v>16.86639393</v>
+        <v>16.84416636</v>
       </c>
       <c r="O53">
-        <v>3.373278786</v>
+        <v>3.368833272</v>
       </c>
       <c r="P53">
-        <v>13.493115144</v>
+        <v>13.475333088</v>
       </c>
       <c r="Q53">
-        <v>14.293115144</v>
+        <v>14.275333088</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1402026272093733</v>
+        <v>0.141954717543623</v>
       </c>
       <c r="T53">
-        <v>1.790782954232894</v>
+        <v>1.824019460436177</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>15.87853177250542</v>
+        <v>15.57317539226493</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08906306442093906</v>
+        <v>0.08890444150928517</v>
       </c>
       <c r="C54">
-        <v>21.20313637870017</v>
+        <v>20.76105198444663</v>
       </c>
       <c r="D54">
-        <v>-1.418063621299839</v>
+        <v>-1.418248015553371</v>
       </c>
       <c r="E54">
-        <v>16.7888</v>
+        <v>17.2307</v>
       </c>
       <c r="F54">
-        <v>22.9788</v>
+        <v>23.4207</v>
       </c>
       <c r="G54">
         <v>45.6</v>
@@ -5709,28 +5709,28 @@
         <v>18</v>
       </c>
       <c r="M54">
-        <v>1.15583364</v>
+        <v>1.17806121</v>
       </c>
       <c r="N54">
-        <v>16.84416636</v>
+        <v>16.82193879</v>
       </c>
       <c r="O54">
-        <v>3.368833272</v>
+        <v>3.364387758</v>
       </c>
       <c r="P54">
-        <v>13.475333088</v>
+        <v>13.457551032</v>
       </c>
       <c r="Q54">
-        <v>14.275333088</v>
+        <v>14.257551032</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.141954717543623</v>
+        <v>0.1437813649133727</v>
       </c>
       <c r="T54">
-        <v>1.824019460436177</v>
+        <v>1.858670286052366</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>15.57317539226493</v>
+        <v>15.27934189429767</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08890444150928517</v>
+        <v>0.0887458185976313</v>
       </c>
       <c r="C55">
-        <v>20.76105198444663</v>
+        <v>20.31896754223239</v>
       </c>
       <c r="D55">
-        <v>-1.418248015553371</v>
+        <v>-1.418432457767605</v>
       </c>
       <c r="E55">
-        <v>17.2307</v>
+        <v>17.6726</v>
       </c>
       <c r="F55">
-        <v>23.4207</v>
+        <v>23.8626</v>
       </c>
       <c r="G55">
         <v>45.6</v>
@@ -5791,28 +5791,28 @@
         <v>18</v>
       </c>
       <c r="M55">
-        <v>1.17806121</v>
+        <v>1.20028878</v>
       </c>
       <c r="N55">
-        <v>16.82193879</v>
+        <v>16.79971122</v>
       </c>
       <c r="O55">
-        <v>3.364387758</v>
+        <v>3.359942244</v>
       </c>
       <c r="P55">
-        <v>13.457551032</v>
+        <v>13.439768976</v>
       </c>
       <c r="Q55">
-        <v>14.257551032</v>
+        <v>14.239768976</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1437813649133727</v>
+        <v>0.1456874317339811</v>
       </c>
       <c r="T55">
-        <v>1.858670286052366</v>
+        <v>1.894827669304041</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>15.27934189429767</v>
+        <v>14.99639111847734</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0887458185976313</v>
+        <v>0.08858719568597741</v>
       </c>
       <c r="C56">
-        <v>20.31896754223239</v>
+        <v>19.87688305203875</v>
       </c>
       <c r="D56">
-        <v>-1.418432457767605</v>
+        <v>-1.418616947961253</v>
       </c>
       <c r="E56">
-        <v>17.6726</v>
+        <v>18.1145</v>
       </c>
       <c r="F56">
-        <v>23.8626</v>
+        <v>24.3045</v>
       </c>
       <c r="G56">
         <v>45.6</v>
@@ -5873,28 +5873,28 @@
         <v>18</v>
       </c>
       <c r="M56">
-        <v>1.20028878</v>
+        <v>1.22251635</v>
       </c>
       <c r="N56">
-        <v>16.79971122</v>
+        <v>16.77748365</v>
       </c>
       <c r="O56">
-        <v>3.359942244</v>
+        <v>3.35549673</v>
       </c>
       <c r="P56">
-        <v>13.439768976</v>
+        <v>13.42198692</v>
       </c>
       <c r="Q56">
-        <v>14.239768976</v>
+        <v>14.22198692</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1456874317339811</v>
+        <v>0.1476782126355054</v>
       </c>
       <c r="T56">
-        <v>1.894827669304041</v>
+        <v>1.932592047366902</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>14.99639111847734</v>
+        <v>14.72372946177775</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08858719568597741</v>
+        <v>0.08842857277432352</v>
       </c>
       <c r="C57">
-        <v>19.87688305203875</v>
+        <v>19.43479851384696</v>
       </c>
       <c r="D57">
-        <v>-1.418616947961253</v>
+        <v>-1.418801486153041</v>
       </c>
       <c r="E57">
-        <v>18.1145</v>
+        <v>18.5564</v>
       </c>
       <c r="F57">
-        <v>24.3045</v>
+        <v>24.7464</v>
       </c>
       <c r="G57">
         <v>45.6</v>
@@ -5955,28 +5955,28 @@
         <v>18</v>
       </c>
       <c r="M57">
-        <v>1.22251635</v>
+        <v>1.24474392</v>
       </c>
       <c r="N57">
-        <v>16.77748365</v>
+        <v>16.75525608</v>
       </c>
       <c r="O57">
-        <v>3.35549673</v>
+        <v>3.351051216</v>
       </c>
       <c r="P57">
-        <v>13.42198692</v>
+        <v>13.404204864</v>
       </c>
       <c r="Q57">
-        <v>14.22198692</v>
+        <v>14.204204864</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1476782126355054</v>
+        <v>0.149759483578008</v>
       </c>
       <c r="T57">
-        <v>1.932592047366902</v>
+        <v>1.972072988068984</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>14.72372946177775</v>
+        <v>14.46080572138886</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08842857277432352</v>
+        <v>0.08826994986266964</v>
       </c>
       <c r="C58">
-        <v>19.43479851384696</v>
+        <v>18.9927139276383</v>
       </c>
       <c r="D58">
-        <v>-1.418801486153041</v>
+        <v>-1.418986072361701</v>
       </c>
       <c r="E58">
-        <v>18.5564</v>
+        <v>18.9983</v>
       </c>
       <c r="F58">
-        <v>24.7464</v>
+        <v>25.1883</v>
       </c>
       <c r="G58">
         <v>45.6</v>
@@ -6037,28 +6037,28 @@
         <v>18</v>
       </c>
       <c r="M58">
-        <v>1.24474392</v>
+        <v>1.26697149</v>
       </c>
       <c r="N58">
-        <v>16.75525608</v>
+        <v>16.73302851</v>
       </c>
       <c r="O58">
-        <v>3.351051216</v>
+        <v>3.346605702</v>
       </c>
       <c r="P58">
-        <v>13.404204864</v>
+        <v>13.386422808</v>
       </c>
       <c r="Q58">
-        <v>14.204204864</v>
+        <v>14.186422808</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.149759483578008</v>
+        <v>0.151937557820162</v>
       </c>
       <c r="T58">
-        <v>1.972072988068984</v>
+        <v>2.013390251594419</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>14.46080572138886</v>
+        <v>14.20710737539958</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08826994986266964</v>
+        <v>0.08811132695101577</v>
       </c>
       <c r="C59">
-        <v>18.9927139276383</v>
+        <v>18.55062929339402</v>
       </c>
       <c r="D59">
-        <v>-1.418986072361701</v>
+        <v>-1.419170706605978</v>
       </c>
       <c r="E59">
-        <v>18.9983</v>
+        <v>19.4402</v>
       </c>
       <c r="F59">
-        <v>25.1883</v>
+        <v>25.6302</v>
       </c>
       <c r="G59">
         <v>45.6</v>
@@ -6119,28 +6119,28 @@
         <v>18</v>
       </c>
       <c r="M59">
-        <v>1.26697149</v>
+        <v>1.28919906</v>
       </c>
       <c r="N59">
-        <v>16.73302851</v>
+        <v>16.71080094</v>
       </c>
       <c r="O59">
-        <v>3.346605702</v>
+        <v>3.342160188</v>
       </c>
       <c r="P59">
-        <v>13.386422808</v>
+        <v>13.368640752</v>
       </c>
       <c r="Q59">
-        <v>14.186422808</v>
+        <v>14.168640752</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.151937557820162</v>
+        <v>0.1542193498833709</v>
       </c>
       <c r="T59">
-        <v>2.013390251594419</v>
+        <v>2.056675003859159</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>14.20710737539958</v>
+        <v>13.96215724823752</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08811132695101576</v>
+        <v>0.08795270403936188</v>
       </c>
       <c r="C60">
-        <v>18.55062929339403</v>
+        <v>18.10854461109538</v>
       </c>
       <c r="D60">
-        <v>-1.419170706605978</v>
+        <v>-1.419355388904624</v>
       </c>
       <c r="E60">
-        <v>19.4402</v>
+        <v>19.8821</v>
       </c>
       <c r="F60">
-        <v>25.6302</v>
+        <v>26.0721</v>
       </c>
       <c r="G60">
         <v>45.6</v>
@@ -6201,28 +6201,28 @@
         <v>18</v>
       </c>
       <c r="M60">
-        <v>1.28919906</v>
+        <v>1.31142663</v>
       </c>
       <c r="N60">
-        <v>16.71080094</v>
+        <v>16.68857337</v>
       </c>
       <c r="O60">
-        <v>3.342160188</v>
+        <v>3.337714674</v>
       </c>
       <c r="P60">
-        <v>13.368640752</v>
+        <v>13.350858696</v>
       </c>
       <c r="Q60">
-        <v>14.168640752</v>
+        <v>14.150858696</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1542193498833708</v>
+        <v>0.1566124488764924</v>
       </c>
       <c r="T60">
-        <v>2.056675003859159</v>
+        <v>2.102071207453887</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>13.96215724823752</v>
+        <v>13.72551051521655</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08795270403936188</v>
+        <v>0.08779408112770801</v>
       </c>
       <c r="C61">
-        <v>18.10854461109538</v>
+        <v>17.6664598807236</v>
       </c>
       <c r="D61">
-        <v>-1.419355388904624</v>
+        <v>-1.419540119276401</v>
       </c>
       <c r="E61">
-        <v>19.8821</v>
+        <v>20.324</v>
       </c>
       <c r="F61">
-        <v>26.0721</v>
+        <v>26.514</v>
       </c>
       <c r="G61">
         <v>45.6</v>
@@ -6283,28 +6283,28 @@
         <v>18</v>
       </c>
       <c r="M61">
-        <v>1.31142663</v>
+        <v>1.3336542</v>
       </c>
       <c r="N61">
-        <v>16.68857337</v>
+        <v>16.6663458</v>
       </c>
       <c r="O61">
-        <v>3.337714674</v>
+        <v>3.33326916</v>
       </c>
       <c r="P61">
-        <v>13.350858696</v>
+        <v>13.33307664</v>
       </c>
       <c r="Q61">
-        <v>14.150858696</v>
+        <v>14.13307664</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1566124488764924</v>
+        <v>0.15912520281927</v>
       </c>
       <c r="T61">
-        <v>2.102071207453887</v>
+        <v>2.149737221228352</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>13.72551051521655</v>
+        <v>13.49675200662961</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08779408112770801</v>
+        <v>0.08763545821605412</v>
       </c>
       <c r="C62">
-        <v>17.6664598807236</v>
+        <v>17.22437510225992</v>
       </c>
       <c r="D62">
-        <v>-1.419540119276401</v>
+        <v>-1.419724897740085</v>
       </c>
       <c r="E62">
-        <v>20.324</v>
+        <v>20.7659</v>
       </c>
       <c r="F62">
-        <v>26.514</v>
+        <v>26.9559</v>
       </c>
       <c r="G62">
         <v>45.6</v>
@@ -6365,28 +6365,28 @@
         <v>18</v>
       </c>
       <c r="M62">
-        <v>1.3336542</v>
+        <v>1.35588177</v>
       </c>
       <c r="N62">
-        <v>16.6663458</v>
+        <v>16.64411823</v>
       </c>
       <c r="O62">
-        <v>3.33326916</v>
+        <v>3.328823646</v>
       </c>
       <c r="P62">
-        <v>13.33307664</v>
+        <v>13.315294584</v>
       </c>
       <c r="Q62">
-        <v>14.13307664</v>
+        <v>14.115294584</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.15912520281927</v>
+        <v>0.1617668159386003</v>
       </c>
       <c r="T62">
-        <v>2.149737221228352</v>
+        <v>2.19984764596561</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>13.49675200662961</v>
+        <v>13.27549377701273</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08763545821605412</v>
+        <v>0.08747683530440023</v>
       </c>
       <c r="C63">
-        <v>17.22437510225992</v>
+        <v>16.78229027568554</v>
       </c>
       <c r="D63">
-        <v>-1.419724897740085</v>
+        <v>-1.419909724314455</v>
       </c>
       <c r="E63">
-        <v>20.7659</v>
+        <v>21.2078</v>
       </c>
       <c r="F63">
-        <v>26.9559</v>
+        <v>27.3978</v>
       </c>
       <c r="G63">
         <v>45.6</v>
@@ -6447,28 +6447,28 @@
         <v>18</v>
       </c>
       <c r="M63">
-        <v>1.35588177</v>
+        <v>1.37810934</v>
       </c>
       <c r="N63">
-        <v>16.64411823</v>
+        <v>16.62189066</v>
       </c>
       <c r="O63">
-        <v>3.328823646</v>
+        <v>3.324378132</v>
       </c>
       <c r="P63">
-        <v>13.315294584</v>
+        <v>13.297512528</v>
       </c>
       <c r="Q63">
-        <v>14.115294584</v>
+        <v>14.097512528</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1617668159386003</v>
+        <v>0.1645474613273691</v>
       </c>
       <c r="T63">
-        <v>2.19984764596561</v>
+        <v>2.252595461478512</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>13.27549377701273</v>
+        <v>13.06137290964155</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08747683530440023</v>
+        <v>0.08807421239274636</v>
       </c>
       <c r="C64">
-        <v>16.78229027568554</v>
+        <v>16.34108608577258</v>
       </c>
       <c r="D64">
-        <v>-1.419909724314455</v>
+        <v>-1.419213914227426</v>
       </c>
       <c r="E64">
-        <v>21.2078</v>
+        <v>21.6497</v>
       </c>
       <c r="F64">
-        <v>27.3978</v>
+        <v>27.8397</v>
       </c>
       <c r="G64">
         <v>45.6</v>
@@ -6529,45 +6529,45 @@
         <v>18</v>
       </c>
       <c r="M64">
-        <v>1.37810934</v>
+        <v>1.44209646</v>
       </c>
       <c r="N64">
-        <v>16.62189066</v>
+        <v>16.55790354</v>
       </c>
       <c r="O64">
-        <v>3.324378132</v>
+        <v>3.311580708000001</v>
       </c>
       <c r="P64">
-        <v>13.297512528</v>
+        <v>13.246322832</v>
       </c>
       <c r="Q64">
-        <v>14.097512528</v>
+        <v>14.046322832</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1645474613273691</v>
+        <v>0.1674784118722875</v>
       </c>
       <c r="T64">
-        <v>2.252595461478512</v>
+        <v>2.308194510262383</v>
       </c>
       <c r="U64">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V64">
         <v>0.2</v>
       </c>
       <c r="W64">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y64">
-        <v>13.06137290964155</v>
+        <v>12.48182801863337</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08807421239274636</v>
+        <v>0.08792758948109249</v>
       </c>
       <c r="C65">
-        <v>16.34108608577258</v>
+        <v>15.89901536618068</v>
       </c>
       <c r="D65">
-        <v>-1.419213914227426</v>
+        <v>-1.419384633819317</v>
       </c>
       <c r="E65">
-        <v>21.6497</v>
+        <v>22.0916</v>
       </c>
       <c r="F65">
-        <v>27.8397</v>
+        <v>28.2816</v>
       </c>
       <c r="G65">
         <v>45.6</v>
@@ -6611,28 +6611,28 @@
         <v>18</v>
       </c>
       <c r="M65">
-        <v>1.44209646</v>
+        <v>1.46498688</v>
       </c>
       <c r="N65">
-        <v>16.55790354</v>
+        <v>16.53501312</v>
       </c>
       <c r="O65">
-        <v>3.311580708000001</v>
+        <v>3.307002624</v>
       </c>
       <c r="P65">
-        <v>13.246322832</v>
+        <v>13.228010496</v>
       </c>
       <c r="Q65">
-        <v>14.046322832</v>
+        <v>14.028010496</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1674784118722875</v>
+        <v>0.1705721930030347</v>
       </c>
       <c r="T65">
-        <v>2.308194510262383</v>
+        <v>2.366882395089802</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>12.48182801863337</v>
+        <v>12.28679945584223</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08792758948109249</v>
+        <v>0.0877809665694386</v>
       </c>
       <c r="C66">
-        <v>15.89901536618068</v>
+        <v>15.45694460551157</v>
       </c>
       <c r="D66">
-        <v>-1.419384633819317</v>
+        <v>-1.419555394488433</v>
       </c>
       <c r="E66">
-        <v>22.0916</v>
+        <v>22.5335</v>
       </c>
       <c r="F66">
-        <v>28.2816</v>
+        <v>28.7235</v>
       </c>
       <c r="G66">
         <v>45.6</v>
@@ -6693,28 +6693,28 @@
         <v>18</v>
       </c>
       <c r="M66">
-        <v>1.46498688</v>
+        <v>1.4878773</v>
       </c>
       <c r="N66">
-        <v>16.53501312</v>
+        <v>16.5121227</v>
       </c>
       <c r="O66">
-        <v>3.307002624</v>
+        <v>3.30242454</v>
       </c>
       <c r="P66">
-        <v>13.228010496</v>
+        <v>13.20969816</v>
       </c>
       <c r="Q66">
-        <v>14.028010496</v>
+        <v>14.00969816</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1705721930030347</v>
+        <v>0.1738427616269674</v>
       </c>
       <c r="T66">
-        <v>2.366882395089802</v>
+        <v>2.42892387333593</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>12.28679945584223</v>
+        <v>12.09777177190619</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0877809665694386</v>
+        <v>0.08763434365778471</v>
       </c>
       <c r="C67">
-        <v>15.45694460551157</v>
+        <v>15.0148738037504</v>
       </c>
       <c r="D67">
-        <v>-1.419555394488433</v>
+        <v>-1.419726196249603</v>
       </c>
       <c r="E67">
-        <v>22.5335</v>
+        <v>22.9754</v>
       </c>
       <c r="F67">
-        <v>28.7235</v>
+        <v>29.1654</v>
       </c>
       <c r="G67">
         <v>45.6</v>
@@ -6775,28 +6775,28 @@
         <v>18</v>
       </c>
       <c r="M67">
-        <v>1.4878773</v>
+        <v>1.51076772</v>
       </c>
       <c r="N67">
-        <v>16.5121227</v>
+        <v>16.48923228</v>
       </c>
       <c r="O67">
-        <v>3.30242454</v>
+        <v>3.297846456</v>
       </c>
       <c r="P67">
-        <v>13.20969816</v>
+        <v>13.191385824</v>
       </c>
       <c r="Q67">
-        <v>14.00969816</v>
+        <v>13.991385824</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1738427616269674</v>
+        <v>0.1773057166405433</v>
       </c>
       <c r="T67">
-        <v>2.42892387333593</v>
+        <v>2.494614850302419</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>12.09777177190619</v>
+        <v>11.91447219960458</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08763434365778471</v>
+        <v>0.08748772074613084</v>
       </c>
       <c r="C68">
-        <v>15.0148738037504</v>
+        <v>14.57280296088234</v>
       </c>
       <c r="D68">
-        <v>-1.419726196249603</v>
+        <v>-1.419897039117661</v>
       </c>
       <c r="E68">
-        <v>22.9754</v>
+        <v>23.4173</v>
       </c>
       <c r="F68">
-        <v>29.1654</v>
+        <v>29.6073</v>
       </c>
       <c r="G68">
         <v>45.6</v>
@@ -6857,28 +6857,28 @@
         <v>18</v>
       </c>
       <c r="M68">
-        <v>1.51076772</v>
+        <v>1.53365814</v>
       </c>
       <c r="N68">
-        <v>16.48923228</v>
+        <v>16.46634186</v>
       </c>
       <c r="O68">
-        <v>3.297846456</v>
+        <v>3.293268372</v>
       </c>
       <c r="P68">
-        <v>13.191385824</v>
+        <v>13.173073488</v>
       </c>
       <c r="Q68">
-        <v>13.991385824</v>
+        <v>13.973073488</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1773057166405433</v>
+        <v>0.180978547715548</v>
       </c>
       <c r="T68">
-        <v>2.494614850302419</v>
+        <v>2.564287098600211</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>11.91447219960458</v>
+        <v>11.7366442563269</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08748772074613084</v>
+        <v>0.08734109783447695</v>
       </c>
       <c r="C69">
-        <v>14.57280296088234</v>
+        <v>14.13073207689256</v>
       </c>
       <c r="D69">
-        <v>-1.419897039117661</v>
+        <v>-1.420067923107448</v>
       </c>
       <c r="E69">
-        <v>23.4173</v>
+        <v>23.8592</v>
       </c>
       <c r="F69">
-        <v>29.6073</v>
+        <v>30.0492</v>
       </c>
       <c r="G69">
         <v>45.6</v>
@@ -6939,28 +6939,28 @@
         <v>18</v>
       </c>
       <c r="M69">
-        <v>1.53365814</v>
+        <v>1.55654856</v>
       </c>
       <c r="N69">
-        <v>16.46634186</v>
+        <v>16.44345144</v>
       </c>
       <c r="O69">
-        <v>3.293268372</v>
+        <v>3.288690288</v>
       </c>
       <c r="P69">
-        <v>13.173073488</v>
+        <v>13.154761152</v>
       </c>
       <c r="Q69">
-        <v>13.973073488</v>
+        <v>13.954761152</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.180978547715548</v>
+        <v>0.1848809307327405</v>
       </c>
       <c r="T69">
-        <v>2.564287098600211</v>
+        <v>2.638313862416614</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>11.7366442563269</v>
+        <v>11.56404654667504</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08734109783447695</v>
+        <v>0.08719447492282306</v>
       </c>
       <c r="C70">
-        <v>14.13073207689256</v>
+        <v>13.68866115176619</v>
       </c>
       <c r="D70">
-        <v>-1.420067923107448</v>
+        <v>-1.420238848233814</v>
       </c>
       <c r="E70">
-        <v>23.8592</v>
+        <v>24.3011</v>
       </c>
       <c r="F70">
-        <v>30.0492</v>
+        <v>30.4911</v>
       </c>
       <c r="G70">
         <v>45.6</v>
@@ -7021,28 +7021,28 @@
         <v>18</v>
       </c>
       <c r="M70">
-        <v>1.55654856</v>
+        <v>1.57943898</v>
       </c>
       <c r="N70">
-        <v>16.44345144</v>
+        <v>16.42056102</v>
       </c>
       <c r="O70">
-        <v>3.288690288</v>
+        <v>3.284112204</v>
       </c>
       <c r="P70">
-        <v>13.154761152</v>
+        <v>13.136448816</v>
       </c>
       <c r="Q70">
-        <v>13.954761152</v>
+        <v>13.936448816</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1848809307327405</v>
+        <v>0.1890350803962035</v>
       </c>
       <c r="T70">
-        <v>2.638313862416614</v>
+        <v>2.717116546479237</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>11.56404654667504</v>
+        <v>11.39645166918699</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08719447492282306</v>
+        <v>0.08704785201116919</v>
       </c>
       <c r="C71">
-        <v>13.68866115176619</v>
+        <v>13.24659018548839</v>
       </c>
       <c r="D71">
-        <v>-1.420238848233814</v>
+        <v>-1.420409814511613</v>
       </c>
       <c r="E71">
-        <v>24.3011</v>
+        <v>24.743</v>
       </c>
       <c r="F71">
-        <v>30.4911</v>
+        <v>30.933</v>
       </c>
       <c r="G71">
         <v>45.6</v>
@@ -7103,28 +7103,28 @@
         <v>18</v>
       </c>
       <c r="M71">
-        <v>1.57943898</v>
+        <v>1.6023294</v>
       </c>
       <c r="N71">
-        <v>16.42056102</v>
+        <v>16.3976706</v>
       </c>
       <c r="O71">
-        <v>3.284112204</v>
+        <v>3.279534120000001</v>
       </c>
       <c r="P71">
-        <v>13.136448816</v>
+        <v>13.11813648</v>
       </c>
       <c r="Q71">
-        <v>13.936448816</v>
+        <v>13.91813648</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1890350803962035</v>
+        <v>0.193466173370564</v>
       </c>
       <c r="T71">
-        <v>2.717116546479237</v>
+        <v>2.801172742812701</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>11.39645166918699</v>
+        <v>11.23364521677004</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08704785201116919</v>
+        <v>0.08690122909951531</v>
       </c>
       <c r="C72">
-        <v>13.24659018548839</v>
+        <v>12.80451917804429</v>
       </c>
       <c r="D72">
-        <v>-1.420409814511613</v>
+        <v>-1.420580821955709</v>
       </c>
       <c r="E72">
-        <v>24.743</v>
+        <v>25.1849</v>
       </c>
       <c r="F72">
-        <v>30.933</v>
+        <v>31.3749</v>
       </c>
       <c r="G72">
         <v>45.6</v>
@@ -7185,28 +7185,28 @@
         <v>18</v>
       </c>
       <c r="M72">
-        <v>1.6023294</v>
+        <v>1.62521982</v>
       </c>
       <c r="N72">
-        <v>16.3976706</v>
+        <v>16.37478018</v>
       </c>
       <c r="O72">
-        <v>3.279534120000001</v>
+        <v>3.274956036000001</v>
       </c>
       <c r="P72">
-        <v>13.11813648</v>
+        <v>13.099824144</v>
       </c>
       <c r="Q72">
-        <v>13.91813648</v>
+        <v>13.899824144</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.193466173370564</v>
+        <v>0.1982028589638459</v>
       </c>
       <c r="T72">
-        <v>2.801172742812701</v>
+        <v>2.891025918203647</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>11.23364521677004</v>
+        <v>11.07542486160426</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08690122909951531</v>
+        <v>0.08675460618786143</v>
       </c>
       <c r="C73">
-        <v>12.80451917804429</v>
+        <v>12.36244812941903</v>
       </c>
       <c r="D73">
-        <v>-1.420580821955709</v>
+        <v>-1.420751870580973</v>
       </c>
       <c r="E73">
-        <v>25.1849</v>
+        <v>25.6268</v>
       </c>
       <c r="F73">
-        <v>31.3749</v>
+        <v>31.8168</v>
       </c>
       <c r="G73">
         <v>45.6</v>
@@ -7267,28 +7267,28 @@
         <v>18</v>
       </c>
       <c r="M73">
-        <v>1.62521982</v>
+        <v>1.64811024</v>
       </c>
       <c r="N73">
-        <v>16.37478018</v>
+        <v>16.35188976</v>
       </c>
       <c r="O73">
-        <v>3.274956036000001</v>
+        <v>3.270377952</v>
       </c>
       <c r="P73">
-        <v>13.099824144</v>
+        <v>13.081511808</v>
       </c>
       <c r="Q73">
-        <v>13.899824144</v>
+        <v>13.881511808</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1982028589638459</v>
+        <v>0.2032778792423622</v>
       </c>
       <c r="T73">
-        <v>2.891025918203646</v>
+        <v>2.987297177551086</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>11.07542486160426</v>
+        <v>10.9215995163042</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08675460618786143</v>
+        <v>0.08660798327620754</v>
       </c>
       <c r="C74">
-        <v>12.36244812941903</v>
+        <v>11.92037703959772</v>
       </c>
       <c r="D74">
-        <v>-1.420751870580973</v>
+        <v>-1.420922960402281</v>
       </c>
       <c r="E74">
-        <v>25.6268</v>
+        <v>26.0687</v>
       </c>
       <c r="F74">
-        <v>31.8168</v>
+        <v>32.2587</v>
       </c>
       <c r="G74">
         <v>45.6</v>
@@ -7349,28 +7349,28 @@
         <v>18</v>
       </c>
       <c r="M74">
-        <v>1.64811024</v>
+        <v>1.67100066</v>
       </c>
       <c r="N74">
-        <v>16.35188976</v>
+        <v>16.32899934</v>
       </c>
       <c r="O74">
-        <v>3.270377952</v>
+        <v>3.265799868</v>
       </c>
       <c r="P74">
-        <v>13.081511808</v>
+        <v>13.063199472</v>
       </c>
       <c r="Q74">
-        <v>13.881511808</v>
+        <v>13.863199472</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2032778792423622</v>
+        <v>0.2087288269489168</v>
       </c>
       <c r="T74">
-        <v>2.987297177551086</v>
+        <v>3.090699641294633</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>10.9215995163042</v>
+        <v>10.77198856402606</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08660798327620754</v>
+        <v>0.08646136036455367</v>
       </c>
       <c r="C75">
-        <v>11.92037703959772</v>
+        <v>11.47830590856548</v>
       </c>
       <c r="D75">
-        <v>-1.420922960402281</v>
+        <v>-1.421094091434519</v>
       </c>
       <c r="E75">
-        <v>26.0687</v>
+        <v>26.5106</v>
       </c>
       <c r="F75">
-        <v>32.2587</v>
+        <v>32.7006</v>
       </c>
       <c r="G75">
         <v>45.6</v>
@@ -7431,28 +7431,28 @@
         <v>18</v>
       </c>
       <c r="M75">
-        <v>1.67100066</v>
+        <v>1.69389108</v>
       </c>
       <c r="N75">
-        <v>16.32899934</v>
+        <v>16.30610892</v>
       </c>
       <c r="O75">
-        <v>3.265799868</v>
+        <v>3.261221784</v>
       </c>
       <c r="P75">
-        <v>13.063199472</v>
+        <v>13.044887136</v>
       </c>
       <c r="Q75">
-        <v>13.863199472</v>
+        <v>13.844887136</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2087288269489168</v>
+        <v>0.2145990783252064</v>
       </c>
       <c r="T75">
-        <v>3.090699641294633</v>
+        <v>3.202056140710762</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>10.77198856402606</v>
+        <v>10.62642115099868</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08646136036455367</v>
+        <v>0.08631473745289978</v>
       </c>
       <c r="C76">
-        <v>11.47830590856548</v>
+        <v>11.03623473630743</v>
       </c>
       <c r="D76">
-        <v>-1.421094091434519</v>
+        <v>-1.421265263692578</v>
       </c>
       <c r="E76">
-        <v>26.5106</v>
+        <v>26.9525</v>
       </c>
       <c r="F76">
-        <v>32.7006</v>
+        <v>33.1425</v>
       </c>
       <c r="G76">
         <v>45.6</v>
@@ -7513,28 +7513,28 @@
         <v>18</v>
       </c>
       <c r="M76">
-        <v>1.69389108</v>
+        <v>1.7167815</v>
       </c>
       <c r="N76">
-        <v>16.30610892</v>
+        <v>16.2832185</v>
       </c>
       <c r="O76">
-        <v>3.261221784</v>
+        <v>3.2566437</v>
       </c>
       <c r="P76">
-        <v>13.044887136</v>
+        <v>13.0265748</v>
       </c>
       <c r="Q76">
-        <v>13.844887136</v>
+        <v>13.8265748</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2145990783252064</v>
+        <v>0.2209389498115991</v>
       </c>
       <c r="T76">
-        <v>3.202056140710762</v>
+        <v>3.32232116008018</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>10.62642115099868</v>
+        <v>10.48473553565203</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08631473745289978</v>
+        <v>0.0861681145412459</v>
       </c>
       <c r="C77">
-        <v>11.03623473630743</v>
+        <v>10.59416352280865</v>
       </c>
       <c r="D77">
-        <v>-1.421265263692578</v>
+        <v>-1.421436477191355</v>
       </c>
       <c r="E77">
-        <v>26.9525</v>
+        <v>27.39439999999999</v>
       </c>
       <c r="F77">
-        <v>33.1425</v>
+        <v>33.5844</v>
       </c>
       <c r="G77">
         <v>45.6</v>
@@ -7595,28 +7595,28 @@
         <v>18</v>
       </c>
       <c r="M77">
-        <v>1.7167815</v>
+        <v>1.73967192</v>
       </c>
       <c r="N77">
-        <v>16.2832185</v>
+        <v>16.26032808</v>
       </c>
       <c r="O77">
-        <v>3.2566437</v>
+        <v>3.252065616</v>
       </c>
       <c r="P77">
-        <v>13.0265748</v>
+        <v>13.008262464</v>
       </c>
       <c r="Q77">
-        <v>13.8265748</v>
+        <v>13.808262464</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2209389498115991</v>
+        <v>0.2278071439218579</v>
       </c>
       <c r="T77">
-        <v>3.32232116008018</v>
+        <v>3.45260826439705</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>10.48473553565203</v>
+        <v>10.3467784891303</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0861681145412459</v>
+        <v>0.08602149162959201</v>
       </c>
       <c r="C78">
-        <v>10.59416352280865</v>
+        <v>10.15209226805424</v>
       </c>
       <c r="D78">
-        <v>-1.421436477191355</v>
+        <v>-1.421607731945759</v>
       </c>
       <c r="E78">
-        <v>27.39439999999999</v>
+        <v>27.8363</v>
       </c>
       <c r="F78">
-        <v>33.5844</v>
+        <v>34.0263</v>
       </c>
       <c r="G78">
         <v>45.6</v>
@@ -7677,28 +7677,28 @@
         <v>18</v>
       </c>
       <c r="M78">
-        <v>1.73967192</v>
+        <v>1.76256234</v>
       </c>
       <c r="N78">
-        <v>16.26032808</v>
+        <v>16.23743766</v>
       </c>
       <c r="O78">
-        <v>3.252065616</v>
+        <v>3.247487532000001</v>
       </c>
       <c r="P78">
-        <v>13.008262464</v>
+        <v>12.989950128</v>
       </c>
       <c r="Q78">
-        <v>13.808262464</v>
+        <v>13.789950128</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2278071439218579</v>
+        <v>0.235272572302574</v>
       </c>
       <c r="T78">
-        <v>3.45260826439705</v>
+        <v>3.594224682132778</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>10.3467784891303</v>
+        <v>10.21240474251822</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08602149162959201</v>
+        <v>0.08587486871793813</v>
       </c>
       <c r="C79">
-        <v>10.15209226805424</v>
+        <v>9.710020972029305</v>
       </c>
       <c r="D79">
-        <v>-1.421607731945759</v>
+        <v>-1.421779027970702</v>
       </c>
       <c r="E79">
-        <v>27.8363</v>
+        <v>28.27819999999999</v>
       </c>
       <c r="F79">
-        <v>34.0263</v>
+        <v>34.4682</v>
       </c>
       <c r="G79">
         <v>45.6</v>
@@ -7759,28 +7759,28 @@
         <v>18</v>
       </c>
       <c r="M79">
-        <v>1.76256234</v>
+        <v>1.78545276</v>
       </c>
       <c r="N79">
-        <v>16.23743766</v>
+        <v>16.21454724</v>
       </c>
       <c r="O79">
-        <v>3.247487532000001</v>
+        <v>3.242909448000001</v>
       </c>
       <c r="P79">
-        <v>12.989950128</v>
+        <v>12.971637792</v>
       </c>
       <c r="Q79">
-        <v>13.789950128</v>
+        <v>13.771637792</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.235272572302574</v>
+        <v>0.2434166759906279</v>
       </c>
       <c r="T79">
-        <v>3.594224682132778</v>
+        <v>3.748715319662664</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>10.21240474251822</v>
+        <v>10.0814764765885</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08587486871793813</v>
+        <v>0.08572824580628424</v>
       </c>
       <c r="C80">
-        <v>9.710020972029305</v>
+        <v>9.267949634718896</v>
       </c>
       <c r="D80">
-        <v>-1.421779027970702</v>
+        <v>-1.421950365281105</v>
       </c>
       <c r="E80">
-        <v>28.27819999999999</v>
+        <v>28.7201</v>
       </c>
       <c r="F80">
-        <v>34.4682</v>
+        <v>34.9101</v>
       </c>
       <c r="G80">
         <v>45.6</v>
@@ -7841,28 +7841,28 @@
         <v>18</v>
       </c>
       <c r="M80">
-        <v>1.78545276</v>
+        <v>1.80834318</v>
       </c>
       <c r="N80">
-        <v>16.21454724</v>
+        <v>16.19165682</v>
       </c>
       <c r="O80">
-        <v>3.242909448000001</v>
+        <v>3.238331364</v>
       </c>
       <c r="P80">
-        <v>12.971637792</v>
+        <v>12.953325456</v>
       </c>
       <c r="Q80">
-        <v>13.771637792</v>
+        <v>13.753325456</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2434166759906279</v>
+        <v>0.2523364086013536</v>
       </c>
       <c r="T80">
-        <v>3.748715319662664</v>
+        <v>3.917919351243014</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>10.0814764765885</v>
+        <v>9.953862850302562</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08572824580628424</v>
+        <v>0.08558162289463037</v>
       </c>
       <c r="C81">
-        <v>9.267949634718896</v>
+        <v>8.825878256108112</v>
       </c>
       <c r="D81">
-        <v>-1.421950365281105</v>
+        <v>-1.422121743891894</v>
       </c>
       <c r="E81">
-        <v>28.7201</v>
+        <v>29.162</v>
       </c>
       <c r="F81">
-        <v>34.9101</v>
+        <v>35.352</v>
       </c>
       <c r="G81">
         <v>45.6</v>
@@ -7923,28 +7923,28 @@
         <v>18</v>
       </c>
       <c r="M81">
-        <v>1.80834318</v>
+        <v>1.8312336</v>
       </c>
       <c r="N81">
-        <v>16.19165682</v>
+        <v>16.1687664</v>
       </c>
       <c r="O81">
-        <v>3.238331364</v>
+        <v>3.23375328</v>
       </c>
       <c r="P81">
-        <v>12.953325456</v>
+        <v>12.93501312</v>
       </c>
       <c r="Q81">
-        <v>13.753325456</v>
+        <v>13.73501312</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2523364086013536</v>
+        <v>0.2621481144731518</v>
       </c>
       <c r="T81">
-        <v>3.917919351243014</v>
+        <v>4.1040437859814</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>9.953862850302562</v>
+        <v>9.82943956467378</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08558162289463037</v>
+        <v>0.08653659998297647</v>
       </c>
       <c r="C82">
-        <v>8.825878256108112</v>
+        <v>8.385093729686623</v>
       </c>
       <c r="D82">
-        <v>-1.422121743891894</v>
+        <v>-1.421006270313375</v>
       </c>
       <c r="E82">
-        <v>29.162</v>
+        <v>29.6039</v>
       </c>
       <c r="F82">
-        <v>35.352</v>
+        <v>35.7939</v>
       </c>
       <c r="G82">
         <v>45.6</v>
@@ -8005,45 +8005,45 @@
         <v>18</v>
       </c>
       <c r="M82">
-        <v>1.8312336</v>
+        <v>1.91497365</v>
       </c>
       <c r="N82">
-        <v>16.1687664</v>
+        <v>16.08502635</v>
       </c>
       <c r="O82">
-        <v>3.23375328</v>
+        <v>3.21700527</v>
       </c>
       <c r="P82">
-        <v>12.93501312</v>
+        <v>12.86802108</v>
       </c>
       <c r="Q82">
-        <v>13.73501312</v>
+        <v>13.66802108</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2621481144731518</v>
+        <v>0.2729926314893499</v>
       </c>
       <c r="T82">
-        <v>4.1040437859814</v>
+        <v>4.309760266481721</v>
       </c>
       <c r="U82">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V82">
         <v>0.2</v>
       </c>
       <c r="W82">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y82">
-        <v>9.82943956467378</v>
+        <v>9.399607143419439</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08653659998297647</v>
+        <v>0.0864035770713226</v>
       </c>
       <c r="C83">
-        <v>8.385093729686623</v>
+        <v>7.943038455431015</v>
       </c>
       <c r="D83">
-        <v>-1.421006270313375</v>
+        <v>-1.42116154456899</v>
       </c>
       <c r="E83">
-        <v>29.6039</v>
+        <v>30.0458</v>
       </c>
       <c r="F83">
-        <v>35.7939</v>
+        <v>36.2358</v>
       </c>
       <c r="G83">
         <v>45.6</v>
@@ -8087,28 +8087,28 @@
         <v>18</v>
       </c>
       <c r="M83">
-        <v>1.91497365</v>
+        <v>1.9386153</v>
       </c>
       <c r="N83">
-        <v>16.08502635</v>
+        <v>16.0613847</v>
       </c>
       <c r="O83">
-        <v>3.21700527</v>
+        <v>3.212276940000001</v>
       </c>
       <c r="P83">
-        <v>12.86802108</v>
+        <v>12.84910776</v>
       </c>
       <c r="Q83">
-        <v>13.66802108</v>
+        <v>13.64910776</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2729926314893499</v>
+        <v>0.2850420948406812</v>
       </c>
       <c r="T83">
-        <v>4.309760266481721</v>
+        <v>4.538334133704299</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>9.399607143419439</v>
+        <v>9.284977788011888</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.0864035770713226</v>
+        <v>0.08627055415966872</v>
       </c>
       <c r="C84">
-        <v>7.943038455431015</v>
+        <v>7.500983147237854</v>
       </c>
       <c r="D84">
-        <v>-1.42116154456899</v>
+        <v>-1.421316852762145</v>
       </c>
       <c r="E84">
-        <v>30.0458</v>
+        <v>30.4877</v>
       </c>
       <c r="F84">
-        <v>36.2358</v>
+        <v>36.6777</v>
       </c>
       <c r="G84">
         <v>45.6</v>
@@ -8169,28 +8169,28 @@
         <v>18</v>
       </c>
       <c r="M84">
-        <v>1.9386153</v>
+        <v>1.96225695</v>
       </c>
       <c r="N84">
-        <v>16.0613847</v>
+        <v>16.03774305</v>
       </c>
       <c r="O84">
-        <v>3.212276940000001</v>
+        <v>3.20754861</v>
       </c>
       <c r="P84">
-        <v>12.84910776</v>
+        <v>12.83019444</v>
       </c>
       <c r="Q84">
-        <v>13.64910776</v>
+        <v>13.63019444</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2850420948406812</v>
+        <v>0.2985091421156985</v>
       </c>
       <c r="T84">
-        <v>4.538334133704299</v>
+        <v>4.793799044129536</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>9.284977788011888</v>
+        <v>9.173110585746683</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08627055415966872</v>
+        <v>0.08613753124801485</v>
       </c>
       <c r="C85">
-        <v>7.500983147237854</v>
+        <v>7.058927805096033</v>
       </c>
       <c r="D85">
-        <v>-1.421316852762145</v>
+        <v>-1.42147219490397</v>
       </c>
       <c r="E85">
-        <v>30.4877</v>
+        <v>30.9296</v>
       </c>
       <c r="F85">
-        <v>36.6777</v>
+        <v>37.1196</v>
       </c>
       <c r="G85">
         <v>45.6</v>
@@ -8251,28 +8251,28 @@
         <v>18</v>
       </c>
       <c r="M85">
-        <v>1.96225695</v>
+        <v>1.9858986</v>
       </c>
       <c r="N85">
-        <v>16.03774305</v>
+        <v>16.0141014</v>
       </c>
       <c r="O85">
-        <v>3.20754861</v>
+        <v>3.202820280000001</v>
       </c>
       <c r="P85">
-        <v>12.83019444</v>
+        <v>12.81128112</v>
       </c>
       <c r="Q85">
-        <v>13.63019444</v>
+        <v>13.61128112</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2985091421156985</v>
+        <v>0.3136595703000929</v>
       </c>
       <c r="T85">
-        <v>4.793799044129536</v>
+        <v>5.081197068357925</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>9.173110585746683</v>
+        <v>9.063906888297319</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08613753124801485</v>
+        <v>0.08600450833636096</v>
       </c>
       <c r="C86">
-        <v>7.058927805096033</v>
+        <v>6.616872428994412</v>
       </c>
       <c r="D86">
-        <v>-1.42147219490397</v>
+        <v>-1.421627571005595</v>
       </c>
       <c r="E86">
-        <v>30.9296</v>
+        <v>31.37149999999999</v>
       </c>
       <c r="F86">
-        <v>37.1196</v>
+        <v>37.5615</v>
       </c>
       <c r="G86">
         <v>45.6</v>
@@ -8333,28 +8333,28 @@
         <v>18</v>
       </c>
       <c r="M86">
-        <v>1.9858986</v>
+        <v>2.00954025</v>
       </c>
       <c r="N86">
-        <v>16.0141014</v>
+        <v>15.99045975</v>
       </c>
       <c r="O86">
-        <v>3.202820280000001</v>
+        <v>3.19809195</v>
       </c>
       <c r="P86">
-        <v>12.81128112</v>
+        <v>12.7923678</v>
       </c>
       <c r="Q86">
-        <v>13.61128112</v>
+        <v>13.5923678</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3136595703000927</v>
+        <v>0.3308300555757397</v>
       </c>
       <c r="T86">
-        <v>5.081197068357922</v>
+        <v>5.406914829150097</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>9.063906888297319</v>
+        <v>8.957272689611468</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08600450833636096</v>
+        <v>0.08587148542470707</v>
       </c>
       <c r="C87">
-        <v>6.616872428994412</v>
+        <v>6.174817018921843</v>
       </c>
       <c r="D87">
-        <v>-1.421627571005595</v>
+        <v>-1.421782981078158</v>
       </c>
       <c r="E87">
-        <v>31.37149999999999</v>
+        <v>31.8134</v>
       </c>
       <c r="F87">
-        <v>37.5615</v>
+        <v>38.0034</v>
       </c>
       <c r="G87">
         <v>45.6</v>
@@ -8415,28 +8415,28 @@
         <v>18</v>
       </c>
       <c r="M87">
-        <v>2.00954025</v>
+        <v>2.0331819</v>
       </c>
       <c r="N87">
-        <v>15.99045975</v>
+        <v>15.9668181</v>
       </c>
       <c r="O87">
-        <v>3.19809195</v>
+        <v>3.19336362</v>
       </c>
       <c r="P87">
-        <v>12.7923678</v>
+        <v>12.77345448</v>
       </c>
       <c r="Q87">
-        <v>13.5923678</v>
+        <v>13.57345448</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3308300555757397</v>
+        <v>0.3504534673193362</v>
       </c>
       <c r="T87">
-        <v>5.406914829150097</v>
+        <v>5.779163698626868</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>8.957272689611468</v>
+        <v>8.853118356011336</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08587148542470707</v>
+        <v>0.0857384625130532</v>
       </c>
       <c r="C88">
-        <v>6.174817018921843</v>
+        <v>5.732761574867205</v>
       </c>
       <c r="D88">
-        <v>-1.421782981078158</v>
+        <v>-1.421938425132802</v>
       </c>
       <c r="E88">
-        <v>31.8134</v>
+        <v>32.2553</v>
       </c>
       <c r="F88">
-        <v>38.0034</v>
+        <v>38.4453</v>
       </c>
       <c r="G88">
         <v>45.6</v>
@@ -8497,28 +8497,28 @@
         <v>18</v>
       </c>
       <c r="M88">
-        <v>2.0331819</v>
+        <v>2.05682355</v>
       </c>
       <c r="N88">
-        <v>15.9668181</v>
+        <v>15.94317645</v>
       </c>
       <c r="O88">
-        <v>3.19336362</v>
+        <v>3.18863529</v>
       </c>
       <c r="P88">
-        <v>12.77345448</v>
+        <v>12.75454116</v>
       </c>
       <c r="Q88">
-        <v>13.57345448</v>
+        <v>13.55454116</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3504534673193362</v>
+        <v>0.3730958654850245</v>
       </c>
       <c r="T88">
-        <v>5.779163698626868</v>
+        <v>6.208681624946219</v>
       </c>
       <c r="U88">
         <v>0.0535</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>8.853118356011336</v>
+        <v>8.751358374907756</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0857384625130532</v>
+        <v>0.08560543960139931</v>
       </c>
       <c r="C89">
-        <v>5.732761574867205</v>
+        <v>5.290706096819328</v>
       </c>
       <c r="D89">
-        <v>-1.421938425132802</v>
+        <v>-1.422093903180673</v>
       </c>
       <c r="E89">
-        <v>32.2553</v>
+        <v>32.6972</v>
       </c>
       <c r="F89">
-        <v>38.4453</v>
+        <v>38.8872</v>
       </c>
       <c r="G89">
         <v>45.6</v>
@@ -8579,28 +8579,28 @@
         <v>18</v>
       </c>
       <c r="M89">
-        <v>2.05682355</v>
+        <v>2.0804652</v>
       </c>
       <c r="N89">
-        <v>15.94317645</v>
+        <v>15.9195348</v>
       </c>
       <c r="O89">
-        <v>3.18863529</v>
+        <v>3.18390696</v>
       </c>
       <c r="P89">
-        <v>12.75454116</v>
+        <v>12.73562784</v>
       </c>
       <c r="Q89">
-        <v>13.55454116</v>
+        <v>13.53562784</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3730958654850245</v>
+        <v>0.3995119966783276</v>
       </c>
       <c r="T89">
-        <v>6.208681624946219</v>
+        <v>6.709785872318795</v>
       </c>
       <c r="U89">
         <v>0.0535</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>8.751358374907756</v>
+        <v>8.651911120647441</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08560543960139931</v>
+        <v>0.08547241668974542</v>
       </c>
       <c r="C90">
-        <v>5.290706096819328</v>
+        <v>4.848650584767078</v>
       </c>
       <c r="D90">
-        <v>-1.422093903180673</v>
+        <v>-1.422249415232924</v>
       </c>
       <c r="E90">
-        <v>32.6972</v>
+        <v>33.1391</v>
       </c>
       <c r="F90">
-        <v>38.8872</v>
+        <v>39.3291</v>
       </c>
       <c r="G90">
         <v>45.6</v>
@@ -8661,28 +8661,28 @@
         <v>18</v>
       </c>
       <c r="M90">
-        <v>2.0804652</v>
+        <v>2.10410685</v>
       </c>
       <c r="N90">
-        <v>15.9195348</v>
+        <v>15.89589315</v>
       </c>
       <c r="O90">
-        <v>3.18390696</v>
+        <v>3.17917863</v>
       </c>
       <c r="P90">
-        <v>12.73562784</v>
+        <v>12.71671452</v>
       </c>
       <c r="Q90">
-        <v>13.53562784</v>
+        <v>13.51671452</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3995119966783276</v>
+        <v>0.4307310608158675</v>
       </c>
       <c r="T90">
-        <v>6.709785872318795</v>
+        <v>7.301999982850022</v>
       </c>
       <c r="U90">
         <v>0.0535</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>8.651911120647441</v>
+        <v>8.554698636145783</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08547241668974542</v>
+        <v>0.08533939377809155</v>
       </c>
       <c r="C91">
-        <v>4.848650584767078</v>
+        <v>4.406595038699287</v>
       </c>
       <c r="D91">
-        <v>-1.422249415232924</v>
+        <v>-1.422404961300711</v>
       </c>
       <c r="E91">
-        <v>33.1391</v>
+        <v>33.581</v>
       </c>
       <c r="F91">
-        <v>39.3291</v>
+        <v>39.771</v>
       </c>
       <c r="G91">
         <v>45.6</v>
@@ -8743,28 +8743,28 @@
         <v>18</v>
       </c>
       <c r="M91">
-        <v>2.10410685</v>
+        <v>2.1277485</v>
       </c>
       <c r="N91">
-        <v>15.89589315</v>
+        <v>15.8722515</v>
       </c>
       <c r="O91">
-        <v>3.17917863</v>
+        <v>3.1744503</v>
       </c>
       <c r="P91">
-        <v>12.71671452</v>
+        <v>12.6978012</v>
       </c>
       <c r="Q91">
-        <v>13.51671452</v>
+        <v>13.4978012</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4307310608158675</v>
+        <v>0.4681939377809156</v>
       </c>
       <c r="T91">
-        <v>7.301999982850022</v>
+        <v>8.012656915487495</v>
       </c>
       <c r="U91">
         <v>0.0535</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>8.554698636145783</v>
+        <v>8.459646429077498</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08533939377809155</v>
+        <v>0.08520637086643768</v>
       </c>
       <c r="C92">
-        <v>4.406595038699287</v>
+        <v>3.964539458604811</v>
       </c>
       <c r="D92">
-        <v>-1.422404961300711</v>
+        <v>-1.422560541395195</v>
       </c>
       <c r="E92">
-        <v>33.581</v>
+        <v>34.0229</v>
       </c>
       <c r="F92">
-        <v>39.771</v>
+        <v>40.2129</v>
       </c>
       <c r="G92">
         <v>45.6</v>
@@ -8825,28 +8825,28 @@
         <v>18</v>
       </c>
       <c r="M92">
-        <v>2.1277485</v>
+        <v>2.15139015</v>
       </c>
       <c r="N92">
-        <v>15.8722515</v>
+        <v>15.84860985</v>
       </c>
       <c r="O92">
-        <v>3.1744503</v>
+        <v>3.16972197</v>
       </c>
       <c r="P92">
-        <v>12.6978012</v>
+        <v>12.67888788</v>
       </c>
       <c r="Q92">
-        <v>13.4978012</v>
+        <v>13.47888788</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4681939377809156</v>
+        <v>0.5139818985159742</v>
       </c>
       <c r="T92">
-        <v>8.012656915487495</v>
+        <v>8.881237610933296</v>
       </c>
       <c r="U92">
         <v>0.0535</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>8.459646429077498</v>
+        <v>8.366683281505217</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08520637086643768</v>
+        <v>0.08507334795478379</v>
       </c>
       <c r="C93">
-        <v>3.964539458604811</v>
+        <v>3.522483844472454</v>
       </c>
       <c r="D93">
-        <v>-1.422560541395195</v>
+        <v>-1.422716155527545</v>
       </c>
       <c r="E93">
-        <v>34.0229</v>
+        <v>34.4648</v>
       </c>
       <c r="F93">
-        <v>40.2129</v>
+        <v>40.6548</v>
       </c>
       <c r="G93">
         <v>45.6</v>
@@ -8907,28 +8907,28 @@
         <v>18</v>
       </c>
       <c r="M93">
-        <v>2.15139015</v>
+        <v>2.1750318</v>
       </c>
       <c r="N93">
-        <v>15.84860985</v>
+        <v>15.8249682</v>
       </c>
       <c r="O93">
-        <v>3.16972197</v>
+        <v>3.16499364</v>
       </c>
       <c r="P93">
-        <v>12.67888788</v>
+        <v>12.65997456</v>
       </c>
       <c r="Q93">
-        <v>13.47888788</v>
+        <v>13.45997456</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5139818985159742</v>
+        <v>0.5712168494347976</v>
       </c>
       <c r="T93">
-        <v>8.881237610933296</v>
+        <v>9.966963480240546</v>
       </c>
       <c r="U93">
         <v>0.0535</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>8.366683281505217</v>
+        <v>8.275741071923637</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08507334795478379</v>
+        <v>0.0849403250431299</v>
       </c>
       <c r="C94">
-        <v>3.522483844472454</v>
+        <v>3.080428196291074</v>
       </c>
       <c r="D94">
-        <v>-1.422716155527545</v>
+        <v>-1.422871803708929</v>
       </c>
       <c r="E94">
-        <v>34.4648</v>
+        <v>34.9067</v>
       </c>
       <c r="F94">
-        <v>40.6548</v>
+        <v>41.0967</v>
       </c>
       <c r="G94">
         <v>45.6</v>
@@ -8989,28 +8989,28 @@
         <v>18</v>
       </c>
       <c r="M94">
-        <v>2.1750318</v>
+        <v>2.19867345</v>
       </c>
       <c r="N94">
-        <v>15.8249682</v>
+        <v>15.80132655</v>
       </c>
       <c r="O94">
-        <v>3.16499364</v>
+        <v>3.16026531</v>
       </c>
       <c r="P94">
-        <v>12.65997456</v>
+        <v>12.64106124</v>
       </c>
       <c r="Q94">
-        <v>13.45997456</v>
+        <v>13.44106124</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5712168494347976</v>
+        <v>0.6448046434732846</v>
       </c>
       <c r="T94">
-        <v>9.966963480240546</v>
+        <v>11.36289674077844</v>
       </c>
       <c r="U94">
         <v>0.0535</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>8.275741071923637</v>
+        <v>8.186754608784675</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.0849403250431299</v>
+        <v>0.08480730213147601</v>
       </c>
       <c r="C95">
-        <v>3.080428196291074</v>
+        <v>2.638372514049472</v>
       </c>
       <c r="D95">
-        <v>-1.422871803708929</v>
+        <v>-1.423027485950527</v>
       </c>
       <c r="E95">
-        <v>34.9067</v>
+        <v>35.3486</v>
       </c>
       <c r="F95">
-        <v>41.0967</v>
+        <v>41.5386</v>
       </c>
       <c r="G95">
         <v>45.6</v>
@@ -9071,28 +9071,28 @@
         <v>18</v>
       </c>
       <c r="M95">
-        <v>2.19867345</v>
+        <v>2.2223151</v>
       </c>
       <c r="N95">
-        <v>15.80132655</v>
+        <v>15.7776849</v>
       </c>
       <c r="O95">
-        <v>3.16026531</v>
+        <v>3.15553698</v>
       </c>
       <c r="P95">
-        <v>12.64106124</v>
+        <v>12.62214792</v>
       </c>
       <c r="Q95">
-        <v>13.44106124</v>
+        <v>13.42214792</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6448046434732846</v>
+        <v>0.7429217021912675</v>
       </c>
       <c r="T95">
-        <v>11.36289674077844</v>
+        <v>13.2241410881623</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>8.186754608784675</v>
+        <v>8.099661474648668</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08480730213147601</v>
+        <v>0.08467427921982215</v>
       </c>
       <c r="C96">
-        <v>2.638372514049472</v>
+        <v>2.196316797736486</v>
       </c>
       <c r="D96">
-        <v>-1.423027485950527</v>
+        <v>-1.423183202263517</v>
       </c>
       <c r="E96">
-        <v>35.3486</v>
+        <v>35.7905</v>
       </c>
       <c r="F96">
-        <v>41.5386</v>
+        <v>41.9805</v>
       </c>
       <c r="G96">
         <v>45.6</v>
@@ -9153,28 +9153,28 @@
         <v>18</v>
       </c>
       <c r="M96">
-        <v>2.2223151</v>
+        <v>2.24595675</v>
       </c>
       <c r="N96">
-        <v>15.7776849</v>
+        <v>15.75404325</v>
       </c>
       <c r="O96">
-        <v>3.15553698</v>
+        <v>3.15080865</v>
       </c>
       <c r="P96">
-        <v>12.62214792</v>
+        <v>12.6032346</v>
       </c>
       <c r="Q96">
-        <v>13.42214792</v>
+        <v>13.4032346</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7429217021912675</v>
+        <v>0.880285584396444</v>
       </c>
       <c r="T96">
-        <v>13.2241410881623</v>
+        <v>15.82988317449971</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>8.099661474648668</v>
+        <v>8.014401880178681</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08467427921982215</v>
+        <v>0.08454125630816825</v>
       </c>
       <c r="C97">
-        <v>2.196316797736486</v>
+        <v>1.754261047340911</v>
       </c>
       <c r="D97">
-        <v>-1.423183202263517</v>
+        <v>-1.423338952659087</v>
       </c>
       <c r="E97">
-        <v>35.7905</v>
+        <v>36.23240000000001</v>
       </c>
       <c r="F97">
-        <v>41.9805</v>
+        <v>42.4224</v>
       </c>
       <c r="G97">
         <v>45.6</v>
@@ -9235,28 +9235,28 @@
         <v>18</v>
       </c>
       <c r="M97">
-        <v>2.24595675</v>
+        <v>2.2695984</v>
       </c>
       <c r="N97">
-        <v>15.75404325</v>
+        <v>15.7304016</v>
       </c>
       <c r="O97">
-        <v>3.15080865</v>
+        <v>3.14608032</v>
       </c>
       <c r="P97">
-        <v>12.6032346</v>
+        <v>12.58432128</v>
       </c>
       <c r="Q97">
-        <v>13.4032346</v>
+        <v>13.38432128</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.880285584396444</v>
+        <v>1.086331407704208</v>
       </c>
       <c r="T97">
-        <v>15.82988317449971</v>
+        <v>19.73849630400581</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>8.014401880178681</v>
+        <v>7.930918527260153</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08454125630816828</v>
+        <v>0.08440823339651438</v>
       </c>
       <c r="C98">
-        <v>1.754261047340918</v>
+        <v>1.31220526285157</v>
       </c>
       <c r="D98">
-        <v>-1.423338952659087</v>
+        <v>-1.423494737148428</v>
       </c>
       <c r="E98">
-        <v>36.2324</v>
+        <v>36.6743</v>
       </c>
       <c r="F98">
-        <v>42.4224</v>
+        <v>42.8643</v>
       </c>
       <c r="G98">
         <v>45.6</v>
@@ -9317,28 +9317,28 @@
         <v>18</v>
       </c>
       <c r="M98">
-        <v>2.2695984</v>
+        <v>2.29324005</v>
       </c>
       <c r="N98">
-        <v>15.7304016</v>
+        <v>15.70675995</v>
       </c>
       <c r="O98">
-        <v>3.14608032</v>
+        <v>3.14135199</v>
       </c>
       <c r="P98">
-        <v>12.58432128</v>
+        <v>12.56540796</v>
       </c>
       <c r="Q98">
-        <v>13.38432128</v>
+        <v>13.36540796</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.086331407704206</v>
+        <v>1.429741113217145</v>
       </c>
       <c r="T98">
-        <v>19.73849630400576</v>
+        <v>26.25285151984924</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>7.930918527260155</v>
+        <v>7.849156480587368</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08440823339651438</v>
+        <v>0.08427521048486049</v>
       </c>
       <c r="C99">
-        <v>1.31220526285157</v>
+        <v>0.8701494442572724</v>
       </c>
       <c r="D99">
-        <v>-1.423494737148428</v>
+        <v>-1.423650555742735</v>
       </c>
       <c r="E99">
-        <v>36.6743</v>
+        <v>37.1162</v>
       </c>
       <c r="F99">
-        <v>42.8643</v>
+        <v>43.3062</v>
       </c>
       <c r="G99">
         <v>45.6</v>
@@ -9399,28 +9399,28 @@
         <v>18</v>
       </c>
       <c r="M99">
-        <v>2.29324005</v>
+        <v>2.3168817</v>
       </c>
       <c r="N99">
-        <v>15.70675995</v>
+        <v>15.6831183</v>
       </c>
       <c r="O99">
-        <v>3.14135199</v>
+        <v>3.13662366</v>
       </c>
       <c r="P99">
-        <v>12.56540796</v>
+        <v>12.54649464</v>
       </c>
       <c r="Q99">
-        <v>13.36540796</v>
+        <v>13.34649464</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.429741113217145</v>
+        <v>2.116560524243023</v>
       </c>
       <c r="T99">
-        <v>26.25285151984924</v>
+        <v>39.28156195153621</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>7.849156480587368</v>
+        <v>7.769063047111988</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08427521048486049</v>
+        <v>0.08414218757320661</v>
       </c>
       <c r="C100">
-        <v>0.8701494442572724</v>
+        <v>0.4280935915467907</v>
       </c>
       <c r="D100">
-        <v>-1.423650555742735</v>
+        <v>-1.42380640845321</v>
       </c>
       <c r="E100">
-        <v>37.1162</v>
+        <v>37.5581</v>
       </c>
       <c r="F100">
-        <v>43.3062</v>
+        <v>43.7481</v>
       </c>
       <c r="G100">
         <v>45.6</v>
@@ -9481,28 +9481,28 @@
         <v>18</v>
       </c>
       <c r="M100">
-        <v>2.3168817</v>
+        <v>2.34052335</v>
       </c>
       <c r="N100">
-        <v>15.6831183</v>
+        <v>15.65947665</v>
       </c>
       <c r="O100">
-        <v>3.13662366</v>
+        <v>3.13189533</v>
       </c>
       <c r="P100">
-        <v>12.54649464</v>
+        <v>12.52758132</v>
       </c>
       <c r="Q100">
-        <v>13.34649464</v>
+        <v>13.32758132</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.116560524243023</v>
+        <v>4.177018757320657</v>
       </c>
       <c r="T100">
-        <v>39.28156195153621</v>
+        <v>78.36769324659713</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>7.769063047111988</v>
+        <v>7.690587662797725</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08414218757320661</v>
-      </c>
-      <c r="C101">
-        <v>0.4280935915467907</v>
-      </c>
-      <c r="D101">
-        <v>-1.42380640845321</v>
-      </c>
-      <c r="E101">
-        <v>37.5581</v>
-      </c>
-      <c r="F101">
-        <v>43.7481</v>
-      </c>
-      <c r="G101">
-        <v>45.6</v>
-      </c>
-      <c r="H101">
-        <v>38</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18.8</v>
-      </c>
-      <c r="K101">
-        <v>0.8000000000000007</v>
-      </c>
-      <c r="L101">
-        <v>18</v>
-      </c>
-      <c r="M101">
-        <v>2.34052335</v>
-      </c>
-      <c r="N101">
-        <v>15.65947665</v>
-      </c>
-      <c r="O101">
-        <v>3.13189533</v>
-      </c>
-      <c r="P101">
-        <v>12.52758132</v>
-      </c>
-      <c r="Q101">
-        <v>13.32758132</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.177018757320657</v>
-      </c>
-      <c r="T101">
-        <v>78.36769324659713</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.0428</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>7.690587662797725</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
